--- a/jobs/government_jobs_tracker.xlsx
+++ b/jobs/government_jobs_tracker.xlsx
@@ -1548,7 +1548,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1608,27 +1608,27 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
+          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>08-12-2025</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>08-12-2025</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_15_23_dated_08_12_2025.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_07_07_2026.pdf</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1666,34 +1666,34 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
+          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
+          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_09_05_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_03_24_dated_07_07_2026.pdf</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1731,49 +1731,49 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
+          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 | 23/2026 | Advertisement for regular appointment to the post of Instructor (Electrician/Wireman)/Electrician | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement </t>
+          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/23_2026_0.pdf  </t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_15_23_dated_08_12_2025.pdf</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>BTSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -1786,59 +1786,59 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2 | 23/2026 | Advertisement for regular appointment to the post of Instructor (Electrician/Wireman)/Electrician | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>3 | 22/2026 | Advertisement for regular appointment to the post of Instructor (Electronics Mechanic/Mechanic Radio and TV) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Adv</t>
+          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/22_2026.pdf  </t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_09_05_2026.pdf</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>BTSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
@@ -1851,29 +1851,29 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3 | 22/2026 | Advertisement for regular appointment to the post of Instructor (Electronics Mechanic/Mechanic Radio and TV) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>4 | 21/2026 | Advertisement for regular appointment to the post of Instructor (Fitter) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t xml:space="preserve">2 | 23/2026 | Advertisement for regular appointment to the post of Instructor (Electrician/Wireman)/Electrician | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement </t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/21_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/23_2026_0.pdf  </t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1916,7 +1916,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -1926,19 +1926,19 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4 | 21/2026 | Advertisement for regular appointment to the post of Instructor (Fitter) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>2 | 23/2026 | Advertisement for regular appointment to the post of Instructor (Electrician/Wireman)/Electrician | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>5 | 20/2026 | Advertisement for regular appointment to the post of Instructor (Agriculture and Mechinery) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Adve</t>
+          <t>3 | 22/2026 | Advertisement for regular appointment to the post of Instructor (Electronics Mechanic/Mechanic Radio and TV) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Adv</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/20_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/22_2026.pdf  </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -1991,19 +1991,19 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5 | 20/2026 | Advertisement for regular appointment to the post of Instructor (Agriculture and Mechinery) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>3 | 22/2026 | Advertisement for regular appointment to the post of Instructor (Electronics Mechanic/Mechanic Radio and TV) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>6 | 19/2026 | Advertisement for regular appointment to the post of Instructor (Mechanic Tractor) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement</t>
+          <t>4 | 21/2026 | Advertisement for regular appointment to the post of Instructor (Fitter) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/19_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/21_2026.pdf  </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it , instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2056,19 +2056,19 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6 | 19/2026 | Advertisement for regular appointment to the post of Instructor (Mechanic Tractor) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>4 | 21/2026 | Advertisement for regular appointment to the post of Instructor (Fitter) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>7 | 18/2025 | Advertisement for regular appointment to the post of Instructor (Welder) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>5 | 20/2026 | Advertisement for regular appointment to the post of Instructor (Agriculture and Mechinery) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Adve</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture | Last date appears closed</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2083,7 +2083,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/18_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/20_2026.pdf  </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2111,7 +2111,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture | Last date appears closed</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -2121,19 +2121,19 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>7 | 18/2025 | Advertisement for regular appointment to the post of Instructor (Welder) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>5 | 20/2026 | Advertisement for regular appointment to the post of Instructor (Agriculture and Mechinery) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>8 | 17/2026 | Advertisement for regular appointment to the post of Instructor (Leather Technology) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertiseme</t>
+          <t>6 | 19/2026 | Advertisement for regular appointment to the post of Instructor (Mechanic Tractor) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: leather technology | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/17_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/19_2026.pdf  </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: leather technology | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -2186,19 +2186,19 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>8 | 17/2026 | Advertisement for regular appointment to the post of Instructor (Leather Technology) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>6 | 19/2026 | Advertisement for regular appointment to the post of Instructor (Mechanic Tractor) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>9 | 16/2026 | Advertisement for regular appointment to the post of Instructor (Automobile Engineering/Mechanics) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement</t>
+          <t>7 | 18/2025 | Advertisement for regular appointment to the post of Instructor (Welder) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: automobile | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/16_%202026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/18_2026.pdf  </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: automobile | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -2251,19 +2251,19 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9 | 16/2026 | Advertisement for regular appointment to the post of Instructor (Automobile Engineering/Mechanics) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>7 | 18/2025 | Advertisement for regular appointment to the post of Instructor (Welder) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>10 | 15/2026 | Advertisement for regular appointment to the post of Instructor (Machinist) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Clo</t>
+          <t>8 | 17/2026 | Advertisement for regular appointment to the post of Instructor (Leather Technology) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertiseme</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: leather technology | Last date appears closed</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2278,7 +2278,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/15_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/17_2026.pdf  </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: leather technology | Last date appears closed</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -2316,49 +2316,49 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10 | 15/2026 | Advertisement for regular appointment to the post of Instructor (Machinist) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>8 | 17/2026 | Advertisement for regular appointment to the post of Instructor (Leather Technology) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 17-02-2025 11:30 Hrs Last date for Submission of applications: 17-04-2025 17:30 Hrs (Extended from 18-03-2025 17:30 Hrs)</t>
+          <t>9 | 16/2026 | Advertisement for regular appointment to the post of Instructor (Automobile Engineering/Mechanics) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: automobile | Last date appears closed</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>18-03-2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>18-03-2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/16_%202026.pdf  </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I27" s="2" t="n">
@@ -2371,59 +2371,59 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: automobile | Last date appears closed</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 17-02-2025 11:30 Hrs Last date for Submission of applications: 17-04-2025 17:30 Hrs (Extended from 18-03-2025 17:30 Hrs)</t>
+          <t>9 | 16/2026 | Advertisement for regular appointment to the post of Instructor (Automobile Engineering/Mechanics) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Email ID for general queries recruitment &amp; legal matters uploaded Date 18-12-2025</t>
+          <t>10 | 15/2026 | Advertisement for regular appointment to the post of Instructor (Machinist) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Clo</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>18-12-2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>18-12-2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_dated_18_12_2025.pdf</t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/15_2026.pdf  </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -2436,54 +2436,54 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Email ID for general queries recruitment &amp; legal matters uploaded Date 18-12-2025</t>
+          <t>10 | 15/2026 | Advertisement for regular appointment to the post of Instructor (Machinist) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>1 | 24/2026 | Advertisement for regular appointment to the post of FOOD ANALYST | 20/05/2026 | 19/06/2026 | 19/06/2026 | 19/06/2026 | Advertisement | Advertisement | Closed</t>
+          <t>Start date for Submission of applications: 17-02-2025 11:30 Hrs Last date for Submission of applications: 17-04-2025 17:30 Hrs (Extended from 18-03-2025 17:30 Hrs)</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>18-03-2025</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18-03-2025</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/24_2026.pdf  </t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>BTSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2501,54 +2501,54 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1 | 24/2026 | Advertisement for regular appointment to the post of FOOD ANALYST | 20/05/2026 | 19/06/2026 | 19/06/2026 | 19/06/2026 | Advertisement | Advertisement | Closed</t>
+          <t>Start date for Submission of applications: 17-02-2025 11:30 Hrs Last date for Submission of applications: 17-04-2025 17:30 Hrs (Extended from 18-03-2025 17:30 Hrs)</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
+          <t>Press Release regarding Email ID for general queries recruitment &amp; legal matters uploaded Date 18-12-2025</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>18-12-2025</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>18-12-2025</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819e-ff85f39d0068/publicNotice</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_dated_18_12_2025.pdf</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>HSSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2566,54 +2566,54 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-06-25</t>
+          <t>Press Release regarding Email ID for general queries recruitment &amp; legal matters uploaded Date 18-12-2025</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/</t>
+          <t>1 | 24/2026 | Advertisement for regular appointment to the post of FOOD ANALYST | 20/05/2026 | 19/06/2026 | 19/06/2026 | 19/06/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0506603f0071/publicNotice</t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/24_2026.pdf  </t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>HSSC</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/2026 | 2026-06-26</t>
+          <t>1 | 24/2026 | Advertisement for regular appointment to the post of FOOD ANALYST | 20/05/2026 | 19/06/2026 | 19/06/2026 | 19/06/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0506603f0071/publicNotice</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2706,14 +2706,14 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/2026 | 2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-237201a5007a/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2771,34 +2771,34 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-02</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-237201a5007a/publicNotice</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2836,14 +2836,14 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026 (24-06-2026)</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2853,27 +2853,27 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_P.T._Result_06_26_dated_24_06_2026.pdf</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>HSSC</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2896,49 +2896,49 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026 (24-06-2026)</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Notice regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :25-04-2026</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>25-04-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>25-04-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_08_25_dated_25_04_2026.pdf</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>HSSC</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2956,54 +2956,54 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Notice regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :25-04-2026</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
+          <t>Notice regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :25-04-2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>25-04-2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>26-02-2026</t>
+          <t>25-04-2026</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_08_25_dated_25_04_2026.pdf</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3021,54 +3021,54 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
+          <t>Notice regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :25-04-2026</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Press release regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :26-04-2026</t>
+          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>26-04-2026</t>
+          <t>28-01-2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>26-04-2026</t>
+          <t>26-02-2026</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_08_25_dated_26_04_2026.pdf</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Press release regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :26-04-2026</t>
+          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Combined Civil Services (Backlog) Advt. No.06/2025 Uploaded date:-28-04-2026</t>
+          <t>Press release regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :26-04-2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -3113,17 +3113,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>28-04-2026</t>
+          <t>26-04-2026</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>28-04-2026</t>
+          <t>26-04-2026</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_Instructions_dated_28_04_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_08_25_dated_26_04_2026.pdf</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -3161,7 +3161,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Combined Civil Services (Backlog) Advt. No.06/2025 Uploaded date:-28-04-2026</t>
+          <t>Press release regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :26-04-2026</t>
         </is>
       </c>
     </row>
@@ -4145,7 +4145,7 @@
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Admit Card/Call Letter</t>
+          <t>Recruitments</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -4157,7 +4157,7 @@
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/admit-card</t>
+          <t>https://btsc.bihar.gov.in/index.php/recruitment</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4195,26 +4195,26 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Admit Card/Call Letter</t>
+          <t>Recruitments</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Admit Card/Call Letter</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/website-policies</t>
+          <t>https://btsc.bihar.gov.in/index.php/admit-card</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -4242,7 +4242,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -4252,26 +4252,26 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Admit Card/Call Letter</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Website Policies</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/disclaimer</t>
+          <t>https://btsc.bihar.gov.in/website-policies</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -4309,36 +4309,36 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Website Policies</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconcil</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://btsc.bihar.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>UPPSC</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -4356,36 +4356,36 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconciliation | Modification Start Date Last Date | | |</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Notification Based On OTR</t>
+          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconcil</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>javascript:void();</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -4423,14 +4423,14 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Notification Based On OTR</t>
+          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconciliation | Modification Start Date Last Date | | |</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>View Advertisement</t>
+          <t>Notification Based On OTR</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/OuterPages/View_Advertisement.aspx?ID=114&amp;flag=E</t>
+          <t>javascript:void();</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -4480,26 +4480,26 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>View Advertisement</t>
+          <t>Notification Based On OTR</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>{{'SiteMap_HM' | translate }}</t>
+          <t>View Advertisement</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/FooterPages/SiteMap.aspx</t>
+          <t>https://uppsc.up.nic.in/OuterPages/View_Advertisement.aspx?ID=114&amp;flag=E</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -4537,14 +4537,14 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>{{'SiteMap_HM' | translate }}</t>
+          <t>View Advertisement</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>{{'SiteMap_HM' | translate }}</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -4556,17 +4556,17 @@
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
+          <t>https://uppsc.up.nic.in/FooterPages/SiteMap.aspx</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>UPPSC</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -4589,19 +4589,19 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>{{'SiteMap_HM' | translate }}</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4613,7 +4613,7 @@
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -4628,7 +4628,7 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I65" s="2" t="n">
@@ -4651,14 +4651,14 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -4670,7 +4670,7 @@
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
+          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4685,7 +4685,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -4708,14 +4708,14 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4727,7 +4727,7 @@
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -4765,14 +4765,14 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4784,7 +4784,7 @@
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -4822,14 +4822,14 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4841,7 +4841,7 @@
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
+          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
@@ -4879,36 +4879,36 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
+          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr"/>
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>HSSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -4926,36 +4926,36 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
+          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Apply for CET Group D-05/2026</t>
+          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://onetimeregn.haryana.gov.in/hssc</t>
+          <t>https://hssc.gov.in</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
@@ -4993,26 +4993,26 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Apply for CET Group D-05/2026</t>
+          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Apply for CET Group D-05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/commission</t>
+          <t>https://onetimeregn.haryana.gov.in/hssc</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -5050,83 +5050,83 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Apply for CET Group D-05/2026</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Commission</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
+          <t>https://hssc.gov.in/commission</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>HSSC</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
           <t>https://hssc.gov.in/</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>HSSC</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>General/Other</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>Avoid or Closed</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>https://hssc.gov.in/</t>
-        </is>
-      </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Commission</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/advertisement</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -5164,26 +5164,26 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Recruitment</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Advertisements</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/citizenCharter</t>
+          <t>https://hssc.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -5221,26 +5221,26 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Advertisements</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/notifications</t>
+          <t>https://hssc.gov.in/citizenCharter</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -5278,14 +5278,14 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Apply Online</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -5297,7 +5297,7 @@
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/applyOnline</t>
+          <t>https://hssc.gov.in/notifications</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -5335,26 +5335,26 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Apply Online</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
+          <t>Apply Online</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-37163ea80089/result</t>
+          <t>https://hssc.gov.in/applyOnline</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -5392,14 +5392,14 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
+          <t>Apply Online</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
+          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2b35286b0083/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-37163ea80089/result</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -5449,14 +5449,14 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
+          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -5468,7 +5468,7 @@
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-14153adb0074/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2b35286b0083/result</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -5506,26 +5506,26 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social </t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0315bb59006e/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-14153adb0074/result</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -5563,26 +5563,26 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social Studies (MWT) against Advt. No. 02/2023 and for the posts of TGT Punjabi (ROH) against Advt. No. 04/2023</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
+          <t xml:space="preserve">Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social </t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0275db17006b/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0315bb59006e/result</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -5620,14 +5620,14 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
+          <t>Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social Studies (MWT) against Advt. No. 02/2023 and for the posts of TGT Punjabi (ROH) against Advt. No. 04/2023</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/termsConditions</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0275db17006b/result</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -5677,14 +5677,14 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Statement</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/accessibilityStatement</t>
+          <t>https://hssc.gov.in/termsConditions</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -5734,26 +5734,26 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Statement</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Accessibility Statement</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr"/>
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/disclaimer</t>
+          <t>https://hssc.gov.in/accessibilityStatement</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="K85" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
@@ -5791,14 +5791,14 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Accessibility Statement</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Go to main content</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5810,17 +5810,17 @@
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/#container</t>
+          <t>https://hssc.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>HSSC</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
@@ -5843,31 +5843,31 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Go to main content</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>Go to main content</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/university_constituent.php</t>
+          <t>https://www.jpsc.gov.in/#container</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
@@ -5905,14 +5905,14 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>Go to main content</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -5924,7 +5924,7 @@
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/affilated_religious.php</t>
+          <t>https://www.jpsc.gov.in/university_constituent.php</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5962,14 +5962,14 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -5981,7 +5981,7 @@
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/carrer_uni.php</t>
+          <t>https://www.jpsc.gov.in/affilated_religious.php</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -6019,14 +6019,14 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -6038,7 +6038,7 @@
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/carrer_aff.php</t>
+          <t>https://www.jpsc.gov.in/carrer_uni.php</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -6076,14 +6076,14 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Merit Promotion Scheme</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -6095,7 +6095,7 @@
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/merit_promotion_scheme.php</t>
+          <t>https://www.jpsc.gov.in/carrer_aff.php</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -6133,26 +6133,26 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Merit Promotion Scheme</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Online Application Form (OAS)</t>
+          <t>Merit Promotion Scheme</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/FAQ.pdf</t>
+          <t>https://www.jpsc.gov.in/merit_promotion_scheme.php</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -6190,14 +6190,14 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Online Application Form (OAS)</t>
+          <t>Merit Promotion Scheme</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Online Application</t>
+          <t>Online Application Form (OAS)</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -6209,7 +6209,7 @@
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/?click=yes</t>
+          <t>https://www.jpsc.gov.in/data/FAQ.pdf</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -6247,26 +6247,26 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Online Application</t>
+          <t>Online Application Form (OAS)</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>List of Recognised University/Institution</t>
+          <t>Online Application</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/list_uni.php</t>
+          <t>https://www.jpsc.gov.in/?click=yes</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -6304,14 +6304,14 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>List of Recognised University/Institution</t>
+          <t>Online Application</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
+          <t>List of Recognised University/Institution</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -6323,7 +6323,7 @@
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13044</t>
+          <t>https://www.jpsc.gov.in/list_uni.php</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -6361,14 +6361,14 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
+          <t>List of Recognised University/Institution</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -6380,7 +6380,7 @@
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13043</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13044</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -6418,14 +6418,14 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -6437,7 +6437,7 @@
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13039</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13043</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -6475,14 +6475,14 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13038</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13039</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -6532,14 +6532,14 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
+          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13035</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13038</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I99" s="2" t="n">
@@ -6589,14 +6589,14 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
+          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
+          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6608,7 +6608,7 @@
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13034</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13035</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
@@ -6646,14 +6646,14 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
+          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Director Advt.No.-07/2025</t>
+          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13033</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13034</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -6703,14 +6703,14 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Director Advt.No.-07/2025</t>
+          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
+          <t>Recruitment of Director Advt.No.-07/2025</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13032</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13033</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -6760,14 +6760,14 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
+          <t>Recruitment of Director Advt.No.-07/2025</t>
         </is>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
+          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13031</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13032</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -6817,14 +6817,14 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
+          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
+          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -6836,7 +6836,7 @@
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13030</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13031</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I104" s="2" t="n">
@@ -6874,14 +6874,14 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
+          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
         </is>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6893,7 +6893,7 @@
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13029</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13030</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -6931,14 +6931,14 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
         </is>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6950,7 +6950,7 @@
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13028</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13029</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
@@ -6988,14 +6988,14 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
         </is>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
+          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13026</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13028</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -7045,14 +7045,14 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
+          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
         </is>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
+          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13025</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13026</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -7102,14 +7102,14 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
+          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
         </is>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
+          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -7121,7 +7121,7 @@
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13024</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13025</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
@@ -7159,14 +7159,14 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
+          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
         </is>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
+          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -7178,7 +7178,7 @@
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13021</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13024</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
@@ -7216,14 +7216,14 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
+          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
         </is>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
+          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -7235,7 +7235,7 @@
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13020</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13021</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -7250,7 +7250,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
@@ -7273,14 +7273,14 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
+          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
         </is>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
+          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -7292,7 +7292,7 @@
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=140</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13020</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -7307,7 +7307,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
@@ -7330,14 +7330,14 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
+          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
         </is>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -7349,7 +7349,7 @@
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=134</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=140</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -7387,14 +7387,14 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
         </is>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -7406,7 +7406,7 @@
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=133</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=134</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -7444,26 +7444,26 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
         </is>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
+          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr"/>
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=120</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=133</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L115" s="2" t="inlineStr">
@@ -7501,14 +7501,14 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
+          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
+          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -7520,7 +7520,7 @@
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=119</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=120</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -7558,14 +7558,14 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
+          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
         </is>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
+          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -7577,7 +7577,7 @@
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=118</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=119</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -7615,26 +7615,26 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
+          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
         </is>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
+          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr"/>
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=82</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=118</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="K118" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
         </is>
       </c>
       <c r="L118" s="2" t="inlineStr">
@@ -7672,26 +7672,26 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
+          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
         </is>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
+          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr"/>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=66</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=82</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
@@ -7719,7 +7719,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -7729,26 +7729,26 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
+          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
         </is>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
+          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr"/>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=62</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=66</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -7786,14 +7786,14 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
+          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
         </is>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
+          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=61</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=62</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
@@ -7843,26 +7843,26 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
+          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
         </is>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
+          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr"/>
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=51</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=61</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
         </is>
       </c>
       <c r="L122" s="2" t="inlineStr">
@@ -7900,26 +7900,26 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
+          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
+          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr"/>
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=40</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=51</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -7947,7 +7947,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -7957,14 +7957,14 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
+          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
+          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -7976,7 +7976,7 @@
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=39</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=40</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -8014,26 +8014,26 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
+          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Email Login</t>
+          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr"/>
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in:2096/</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=39</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -8048,7 +8048,7 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="K125" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L125" s="2" t="inlineStr">
@@ -8071,36 +8071,36 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>Email Login</t>
+          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Title | Category Number | Last date</t>
+          <t>Email Login</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr"/>
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications</t>
+          <t>https://www.jpsc.gov.in:2096/</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G126" s="2" t="inlineStr">
         <is>
-          <t>Kerala PSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H126" s="2" t="inlineStr">
@@ -8118,36 +8118,36 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>Title | Category Number | Last date</t>
+          <t>Email Login</t>
         </is>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Title | Category Number | Last date</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr"/>
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications#main-content</t>
+          <t>https://www.keralapsc.gov.in/notifications</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
@@ -8185,26 +8185,26 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Title | Category Number | Last date</t>
         </is>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Answer key-Online Exam</t>
+          <t>Skip to main content</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr"/>
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/answerkey_onlineexams</t>
+          <t>https://www.keralapsc.gov.in/notifications#main-content</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -8232,7 +8232,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -8242,14 +8242,14 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>Answer key-Online Exam</t>
+          <t>Skip to main content</t>
         </is>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Answer key-Online Exam</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       <c r="D129" s="2" t="inlineStr"/>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/notifications</t>
+          <t>https://www.keralapsc.gov.in/answerkey_onlineexams</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -8299,7 +8299,7 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Answer key-Online Exam</t>
         </is>
       </c>
     </row>
@@ -8318,7 +8318,7 @@
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/status_of_advice</t>
+          <t>https://www.keralapsc.gov.in/status_of_advice</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/registration-thrown-out-candidates</t>
+          <t>https://www.keralapsc.gov.in/registration-thrown-out-candidates</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -8432,7 +8432,7 @@
       <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/general-conditions</t>
+          <t>https://www.keralapsc.gov.in/general-conditions</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -9689,27 +9689,27 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
+          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>08-12-2025</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>08-12-2025</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_15_23_dated_08_12_2025.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_07_07_2026.pdf</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -9737,7 +9737,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -9747,34 +9747,34 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
+          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
+          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_09_05_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_03_24_dated_07_07_2026.pdf</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -9802,7 +9802,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -9812,49 +9812,49 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
+          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 | 23/2026 | Advertisement for regular appointment to the post of Instructor (Electrician/Wireman)/Electrician | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement </t>
+          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/23_2026_0.pdf  </t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_15_23_dated_08_12_2025.pdf</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>BTSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
@@ -9867,59 +9867,59 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>2 | 23/2026 | Advertisement for regular appointment to the post of Instructor (Electrician/Wireman)/Electrician | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>3 | 22/2026 | Advertisement for regular appointment to the post of Instructor (Electronics Mechanic/Mechanic Radio and TV) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Adv</t>
+          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/22_2026.pdf  </t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_09_05_2026.pdf</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>BTSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -9932,29 +9932,29 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3 | 22/2026 | Advertisement for regular appointment to the post of Instructor (Electronics Mechanic/Mechanic Radio and TV) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>4 | 21/2026 | Advertisement for regular appointment to the post of Instructor (Fitter) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t xml:space="preserve">2 | 23/2026 | Advertisement for regular appointment to the post of Instructor (Electrician/Wireman)/Electrician | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement </t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -9969,7 +9969,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/21_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/23_2026_0.pdf  </t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -10007,19 +10007,19 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>4 | 21/2026 | Advertisement for regular appointment to the post of Instructor (Fitter) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>2 | 23/2026 | Advertisement for regular appointment to the post of Instructor (Electrician/Wireman)/Electrician | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>5 | 20/2026 | Advertisement for regular appointment to the post of Instructor (Agriculture and Mechinery) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Adve</t>
+          <t>3 | 22/2026 | Advertisement for regular appointment to the post of Instructor (Electronics Mechanic/Mechanic Radio and TV) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Adv</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -10034,7 +10034,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/20_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/22_2026.pdf  </t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -10072,19 +10072,19 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5 | 20/2026 | Advertisement for regular appointment to the post of Instructor (Agriculture and Mechinery) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>3 | 22/2026 | Advertisement for regular appointment to the post of Instructor (Electronics Mechanic/Mechanic Radio and TV) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>6 | 19/2026 | Advertisement for regular appointment to the post of Instructor (Mechanic Tractor) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement</t>
+          <t>4 | 21/2026 | Advertisement for regular appointment to the post of Instructor (Fitter) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/19_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/21_2026.pdf  </t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -10127,7 +10127,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it , instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
@@ -10137,19 +10137,19 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6 | 19/2026 | Advertisement for regular appointment to the post of Instructor (Mechanic Tractor) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>4 | 21/2026 | Advertisement for regular appointment to the post of Instructor (Fitter) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>7 | 18/2025 | Advertisement for regular appointment to the post of Instructor (Welder) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>5 | 20/2026 | Advertisement for regular appointment to the post of Instructor (Agriculture and Mechinery) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Adve</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture | Last date appears closed</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/18_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/20_2026.pdf  </t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture | Last date appears closed</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -10202,19 +10202,19 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7 | 18/2025 | Advertisement for regular appointment to the post of Instructor (Welder) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>5 | 20/2026 | Advertisement for regular appointment to the post of Instructor (Agriculture and Mechinery) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>8 | 17/2026 | Advertisement for regular appointment to the post of Instructor (Leather Technology) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertiseme</t>
+          <t>6 | 19/2026 | Advertisement for regular appointment to the post of Instructor (Mechanic Tractor) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: leather technology | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/17_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/19_2026.pdf  </t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -10257,7 +10257,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: leather technology | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -10267,19 +10267,19 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8 | 17/2026 | Advertisement for regular appointment to the post of Instructor (Leather Technology) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>6 | 19/2026 | Advertisement for regular appointment to the post of Instructor (Mechanic Tractor) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>9 | 16/2026 | Advertisement for regular appointment to the post of Instructor (Automobile Engineering/Mechanics) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement</t>
+          <t>7 | 18/2025 | Advertisement for regular appointment to the post of Instructor (Welder) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: automobile | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/16_%202026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/18_2026.pdf  </t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -10322,7 +10322,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: automobile | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -10332,19 +10332,19 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9 | 16/2026 | Advertisement for regular appointment to the post of Instructor (Automobile Engineering/Mechanics) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>7 | 18/2025 | Advertisement for regular appointment to the post of Instructor (Welder) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>10 | 15/2026 | Advertisement for regular appointment to the post of Instructor (Machinist) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Clo</t>
+          <t>8 | 17/2026 | Advertisement for regular appointment to the post of Instructor (Leather Technology) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertiseme</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: leather technology | Last date appears closed</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/15_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/17_2026.pdf  </t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: leather technology | Last date appears closed</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
@@ -10397,49 +10397,49 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>10 | 15/2026 | Advertisement for regular appointment to the post of Instructor (Machinist) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
+          <t>8 | 17/2026 | Advertisement for regular appointment to the post of Instructor (Leather Technology) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 17-02-2025 11:30 Hrs Last date for Submission of applications: 17-04-2025 17:30 Hrs (Extended from 18-03-2025 17:30 Hrs)</t>
+          <t>9 | 16/2026 | Advertisement for regular appointment to the post of Instructor (Automobile Engineering/Mechanics) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: automobile | Last date appears closed</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>18-03-2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>18-03-2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/16_%202026.pdf  </t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -10452,59 +10452,59 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Specific non-CSE subject appears required | Non-CSE subject risk: automobile | Last date appears closed</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 17-02-2025 11:30 Hrs Last date for Submission of applications: 17-04-2025 17:30 Hrs (Extended from 18-03-2025 17:30 Hrs)</t>
+          <t>9 | 16/2026 | Advertisement for regular appointment to the post of Instructor (Automobile Engineering/Mechanics) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Email ID for general queries recruitment &amp; legal matters uploaded Date 18-12-2025</t>
+          <t>10 | 15/2026 | Advertisement for regular appointment to the post of Instructor (Machinist) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Clo</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>18-12-2025</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>18-12-2025</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_dated_18_12_2025.pdf</t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/15_2026.pdf  </t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I29" s="2" t="n">
@@ -10517,54 +10517,54 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: instructor | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Email ID for general queries recruitment &amp; legal matters uploaded Date 18-12-2025</t>
+          <t>10 | 15/2026 | Advertisement for regular appointment to the post of Instructor (Machinist) | 15/04/2026 | 15/05/2026 | 15/05/2026 | 15/05/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>1 | 24/2026 | Advertisement for regular appointment to the post of FOOD ANALYST | 20/05/2026 | 19/06/2026 | 19/06/2026 | 19/06/2026 | Advertisement | Advertisement | Closed</t>
+          <t>Start date for Submission of applications: 17-02-2025 11:30 Hrs Last date for Submission of applications: 17-04-2025 17:30 Hrs (Extended from 18-03-2025 17:30 Hrs)</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>18-03-2025</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>18-03-2025</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/24_2026.pdf  </t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>BTSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -10582,54 +10582,54 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1 | 24/2026 | Advertisement for regular appointment to the post of FOOD ANALYST | 20/05/2026 | 19/06/2026 | 19/06/2026 | 19/06/2026 | Advertisement | Advertisement | Closed</t>
+          <t>Start date for Submission of applications: 17-02-2025 11:30 Hrs Last date for Submission of applications: 17-04-2025 17:30 Hrs (Extended from 18-03-2025 17:30 Hrs)</t>
         </is>
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
+          <t>Press Release regarding Email ID for general queries recruitment &amp; legal matters uploaded Date 18-12-2025</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>18-12-2025</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>18-12-2025</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819e-ff85f39d0068/publicNotice</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_dated_18_12_2025.pdf</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>HSSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -10647,54 +10647,54 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-06-25</t>
+          <t>Press Release regarding Email ID for general queries recruitment &amp; legal matters uploaded Date 18-12-2025</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/</t>
+          <t>1 | 24/2026 | Advertisement for regular appointment to the post of FOOD ANALYST | 20/05/2026 | 19/06/2026 | 19/06/2026 | 19/06/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0506603f0071/publicNotice</t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/24_2026.pdf  </t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>HSSC</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
@@ -10712,24 +10712,24 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/2026 | 2026-06-26</t>
+          <t>1 | 24/2026 | Advertisement for regular appointment to the post of FOOD ANALYST | 20/05/2026 | 19/06/2026 | 19/06/2026 | 19/06/2026 | Advertisement | Advertisement | Closed</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -10739,17 +10739,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0506603f0071/publicNotice</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -10787,14 +10787,14 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/2026 | 2026-06-26</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-237201a5007a/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -10852,34 +10852,34 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-02</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-237201a5007a/publicNotice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -10907,7 +10907,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -10917,14 +10917,14 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026 (24-06-2026)</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -10934,27 +10934,27 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_P.T._Result_06_26_dated_24_06_2026.pdf</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>HSSC</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -10977,49 +10977,49 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026 (24-06-2026)</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Notice regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :25-04-2026</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>25-04-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>25-04-2026</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_08_25_dated_25_04_2026.pdf</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>HSSC</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -11037,54 +11037,54 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Notice regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :25-04-2026</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
+          <t>Notice regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :25-04-2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>25-04-2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>26-02-2026</t>
+          <t>25-04-2026</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_08_25_dated_25_04_2026.pdf</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -11102,54 +11102,54 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
+          <t>Notice regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :25-04-2026</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Press release regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :26-04-2026</t>
+          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>26-04-2026</t>
+          <t>28-01-2026</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>26-04-2026</t>
+          <t>26-02-2026</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_08_25_dated_26_04_2026.pdf</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -11167,24 +11167,24 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Press release regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :26-04-2026</t>
+          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Combined Civil Services (Backlog) Advt. No.06/2025 Uploaded date:-28-04-2026</t>
+          <t>Press release regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :26-04-2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -11194,17 +11194,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>28-04-2026</t>
+          <t>26-04-2026</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>28-04-2026</t>
+          <t>26-04-2026</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_Instructions_dated_28_04_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_08_25_dated_26_04_2026.pdf</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -11242,7 +11242,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Combined Civil Services (Backlog) Advt. No.06/2025 Uploaded date:-28-04-2026</t>
+          <t>Press release regarding Jharkhand Eligibility Test 2024 Advt.No.08/2025 uploaded date :26-04-2026</t>
         </is>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Admit Card/Call Letter</t>
+          <t>Recruitments</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -12238,7 +12238,7 @@
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/admit-card</t>
+          <t>https://btsc.bihar.gov.in/index.php/recruitment</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -12276,26 +12276,26 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Admit Card/Call Letter</t>
+          <t>Recruitments</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Admit Card/Call Letter</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/website-policies</t>
+          <t>https://btsc.bihar.gov.in/index.php/admit-card</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -12323,7 +12323,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -12333,26 +12333,26 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Admit Card/Call Letter</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Website Policies</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/disclaimer</t>
+          <t>https://btsc.bihar.gov.in/website-policies</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -12380,7 +12380,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -12390,36 +12390,36 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Website Policies</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconcil</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://btsc.bihar.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>UPPSC</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -12437,36 +12437,36 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconciliation | Modification Start Date Last Date | | |</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Notification Based On OTR</t>
+          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconcil</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>javascript:void();</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -12494,7 +12494,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -12504,14 +12504,14 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Notification Based On OTR</t>
+          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconciliation | Modification Start Date Last Date | | |</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>View Advertisement</t>
+          <t>Notification Based On OTR</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -12523,7 +12523,7 @@
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/OuterPages/View_Advertisement.aspx?ID=114&amp;flag=E</t>
+          <t>javascript:void();</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12561,26 +12561,26 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>View Advertisement</t>
+          <t>Notification Based On OTR</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>{{'SiteMap_HM' | translate }}</t>
+          <t>View Advertisement</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/FooterPages/SiteMap.aspx</t>
+          <t>https://uppsc.up.nic.in/OuterPages/View_Advertisement.aspx?ID=114&amp;flag=E</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12608,7 +12608,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -12618,14 +12618,14 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>{{'SiteMap_HM' | translate }}</t>
+          <t>View Advertisement</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>{{'SiteMap_HM' | translate }}</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -12637,17 +12637,17 @@
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
+          <t>https://uppsc.up.nic.in/FooterPages/SiteMap.aspx</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>UPPSC</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -12670,19 +12670,19 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>{{'SiteMap_HM' | translate }}</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -12694,7 +12694,7 @@
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I66" s="2" t="n">
@@ -12732,14 +12732,14 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -12751,7 +12751,7 @@
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
+          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
@@ -12789,14 +12789,14 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -12808,7 +12808,7 @@
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12846,14 +12846,14 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -12865,7 +12865,7 @@
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
@@ -12903,14 +12903,14 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -12922,7 +12922,7 @@
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
+          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12937,7 +12937,7 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
@@ -12960,36 +12960,36 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
+          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>HSSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -13007,36 +13007,36 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
+          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Apply for CET Group D-05/2026</t>
+          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr"/>
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://onetimeregn.haryana.gov.in/hssc</t>
+          <t>https://hssc.gov.in</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
@@ -13074,26 +13074,26 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Apply for CET Group D-05/2026</t>
+          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Apply for CET Group D-05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr"/>
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/commission</t>
+          <t>https://onetimeregn.haryana.gov.in/hssc</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13121,7 +13121,7 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
@@ -13131,83 +13131,83 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Apply for CET Group D-05/2026</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Commission</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
+          <t>https://hssc.gov.in/commission</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>HSSC</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
           <t>https://hssc.gov.in/</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>HSSC</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>General/Other</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>Avoid or Closed</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>https://hssc.gov.in/</t>
-        </is>
-      </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Commission</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/advertisement</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -13245,26 +13245,26 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Recruitment</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Advertisements</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/citizenCharter</t>
+          <t>https://hssc.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13292,7 +13292,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -13302,26 +13302,26 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Advertisements</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/notifications</t>
+          <t>https://hssc.gov.in/citizenCharter</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -13359,14 +13359,14 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Apply Online</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -13378,7 +13378,7 @@
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/applyOnline</t>
+          <t>https://hssc.gov.in/notifications</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13416,26 +13416,26 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Apply Online</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
+          <t>Apply Online</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-37163ea80089/result</t>
+          <t>https://hssc.gov.in/applyOnline</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -13473,14 +13473,14 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
+          <t>Apply Online</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
+          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -13492,7 +13492,7 @@
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2b35286b0083/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-37163ea80089/result</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -13530,14 +13530,14 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
+          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -13549,7 +13549,7 @@
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-14153adb0074/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2b35286b0083/result</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -13587,26 +13587,26 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social </t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0315bb59006e/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-14153adb0074/result</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -13634,7 +13634,7 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
@@ -13644,26 +13644,26 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social Studies (MWT) against Advt. No. 02/2023 and for the posts of TGT Punjabi (ROH) against Advt. No. 04/2023</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
+          <t xml:space="preserve">Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social </t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr"/>
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0275db17006b/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0315bb59006e/result</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="K83" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
@@ -13701,14 +13701,14 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
+          <t>Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social Studies (MWT) against Advt. No. 02/2023 and for the posts of TGT Punjabi (ROH) against Advt. No. 04/2023</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -13720,7 +13720,7 @@
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/termsConditions</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0275db17006b/result</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -13758,14 +13758,14 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Statement</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -13777,7 +13777,7 @@
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/accessibilityStatement</t>
+          <t>https://hssc.gov.in/termsConditions</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -13815,26 +13815,26 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Statement</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Accessibility Statement</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr"/>
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/disclaimer</t>
+          <t>https://hssc.gov.in/accessibilityStatement</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K86" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L86" s="2" t="inlineStr">
@@ -13872,14 +13872,14 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Accessibility Statement</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>Go to main content</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -13891,17 +13891,17 @@
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/#container</t>
+          <t>https://hssc.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>HSSC</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -13924,31 +13924,31 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Go to main content</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>Go to main content</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/university_constituent.php</t>
+          <t>https://www.jpsc.gov.in/#container</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -13976,7 +13976,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -13986,14 +13986,14 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>Go to main content</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -14005,7 +14005,7 @@
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/affilated_religious.php</t>
+          <t>https://www.jpsc.gov.in/university_constituent.php</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -14043,14 +14043,14 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -14062,7 +14062,7 @@
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/carrer_uni.php</t>
+          <t>https://www.jpsc.gov.in/affilated_religious.php</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -14100,14 +14100,14 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -14119,7 +14119,7 @@
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/carrer_aff.php</t>
+          <t>https://www.jpsc.gov.in/carrer_uni.php</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -14157,14 +14157,14 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Merit Promotion Scheme</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -14176,7 +14176,7 @@
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/merit_promotion_scheme.php</t>
+          <t>https://www.jpsc.gov.in/carrer_aff.php</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -14214,26 +14214,26 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Merit Promotion Scheme</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Online Application Form (OAS)</t>
+          <t>Merit Promotion Scheme</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/FAQ.pdf</t>
+          <t>https://www.jpsc.gov.in/merit_promotion_scheme.php</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -14261,7 +14261,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -14271,14 +14271,14 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Online Application Form (OAS)</t>
+          <t>Merit Promotion Scheme</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Online Application</t>
+          <t>Online Application Form (OAS)</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -14290,7 +14290,7 @@
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/?click=yes</t>
+          <t>https://www.jpsc.gov.in/data/FAQ.pdf</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -14328,26 +14328,26 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Online Application</t>
+          <t>Online Application Form (OAS)</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>List of Recognised University/Institution</t>
+          <t>Online Application</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/list_uni.php</t>
+          <t>https://www.jpsc.gov.in/?click=yes</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -14375,7 +14375,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -14385,14 +14385,14 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>List of Recognised University/Institution</t>
+          <t>Online Application</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
+          <t>List of Recognised University/Institution</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -14404,7 +14404,7 @@
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13044</t>
+          <t>https://www.jpsc.gov.in/list_uni.php</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -14442,14 +14442,14 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
+          <t>List of Recognised University/Institution</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -14461,7 +14461,7 @@
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13043</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13044</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -14499,14 +14499,14 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -14518,7 +14518,7 @@
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13039</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13043</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -14556,14 +14556,14 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -14575,7 +14575,7 @@
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13038</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13039</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -14613,14 +14613,14 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
+          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -14632,7 +14632,7 @@
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13035</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13038</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
@@ -14670,14 +14670,14 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
+          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
+          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -14689,7 +14689,7 @@
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13034</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13035</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -14704,7 +14704,7 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -14727,14 +14727,14 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
+          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Director Advt.No.-07/2025</t>
+          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -14746,7 +14746,7 @@
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13033</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13034</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -14784,14 +14784,14 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Director Advt.No.-07/2025</t>
+          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
         </is>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
+          <t>Recruitment of Director Advt.No.-07/2025</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -14803,7 +14803,7 @@
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13032</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13033</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -14841,14 +14841,14 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
+          <t>Recruitment of Director Advt.No.-07/2025</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
+          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -14860,7 +14860,7 @@
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13031</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13032</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -14898,14 +14898,14 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
+          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
         </is>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
+          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -14917,7 +14917,7 @@
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13030</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13031</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -14932,7 +14932,7 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I105" s="2" t="n">
@@ -14955,14 +14955,14 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
+          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
         </is>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -14974,7 +14974,7 @@
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13029</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13030</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -15012,14 +15012,14 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
         </is>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -15031,7 +15031,7 @@
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13028</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13029</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -15046,7 +15046,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I107" s="2" t="n">
@@ -15069,14 +15069,14 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
         </is>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
+          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -15088,7 +15088,7 @@
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13026</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13028</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -15126,14 +15126,14 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
+          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
         </is>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
+          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -15145,7 +15145,7 @@
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13025</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13026</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -15183,14 +15183,14 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
+          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
         </is>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
+          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -15202,7 +15202,7 @@
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13024</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13025</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -15217,7 +15217,7 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I110" s="2" t="n">
@@ -15240,14 +15240,14 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
+          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
         </is>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
+          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -15259,7 +15259,7 @@
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13021</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13024</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I111" s="2" t="n">
@@ -15297,14 +15297,14 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
+          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
         </is>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
+          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -15316,7 +15316,7 @@
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13020</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13021</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I112" s="2" t="n">
@@ -15354,14 +15354,14 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
+          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
         </is>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
+          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -15373,7 +15373,7 @@
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=140</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13020</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -15388,7 +15388,7 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
@@ -15411,14 +15411,14 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
+          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
         </is>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -15430,7 +15430,7 @@
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=134</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=140</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -15468,14 +15468,14 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
         </is>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -15487,7 +15487,7 @@
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=133</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=134</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -15525,26 +15525,26 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
+          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr"/>
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=120</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=133</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="K116" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L116" s="2" t="inlineStr">
@@ -15582,14 +15582,14 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
+          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
         </is>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
+          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -15601,7 +15601,7 @@
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=119</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=120</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -15639,14 +15639,14 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
+          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
         </is>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
+          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -15658,7 +15658,7 @@
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=118</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=119</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -15696,26 +15696,26 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
+          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
         </is>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
+          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr"/>
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=82</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=118</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -15743,7 +15743,7 @@
       </c>
       <c r="K119" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
         </is>
       </c>
       <c r="L119" s="2" t="inlineStr">
@@ -15753,26 +15753,26 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
+          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
         </is>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
+          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr"/>
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=66</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=82</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -15787,7 +15787,7 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I120" s="2" t="n">
@@ -15800,7 +15800,7 @@
       </c>
       <c r="K120" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L120" s="2" t="inlineStr">
@@ -15810,26 +15810,26 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
+          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
         </is>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
+          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr"/>
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=62</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=66</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -15857,7 +15857,7 @@
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="L121" s="2" t="inlineStr">
@@ -15867,14 +15867,14 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
+          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
         </is>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
+          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -15886,7 +15886,7 @@
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=61</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=62</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -15901,7 +15901,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -15924,26 +15924,26 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
+          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
         </is>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
+          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr"/>
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=51</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=61</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -15958,7 +15958,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
@@ -15971,7 +15971,7 @@
       </c>
       <c r="K123" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
         </is>
       </c>
       <c r="L123" s="2" t="inlineStr">
@@ -15981,26 +15981,26 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
+          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
+          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr"/>
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=40</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=51</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -16028,7 +16028,7 @@
       </c>
       <c r="K124" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="L124" s="2" t="inlineStr">
@@ -16038,14 +16038,14 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
+          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
+          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -16057,7 +16057,7 @@
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=39</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=40</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -16095,26 +16095,26 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
+          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Email Login</t>
+          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr"/>
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in:2096/</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=39</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -16129,7 +16129,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
@@ -16142,7 +16142,7 @@
       </c>
       <c r="K126" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L126" s="2" t="inlineStr">
@@ -16152,36 +16152,36 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>Email Login</t>
+          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
         </is>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Title | Category Number | Last date</t>
+          <t>Email Login</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr"/>
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications</t>
+          <t>https://www.jpsc.gov.in:2096/</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G127" s="2" t="inlineStr">
         <is>
-          <t>Kerala PSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H127" s="2" t="inlineStr">
@@ -16199,36 +16199,36 @@
       </c>
       <c r="K127" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L127" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>Title | Category Number | Last date</t>
+          <t>Email Login</t>
         </is>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Title | Category Number | Last date</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr"/>
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications#main-content</t>
+          <t>https://www.keralapsc.gov.in/notifications</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="K128" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L128" s="2" t="inlineStr">
@@ -16266,26 +16266,26 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Title | Category Number | Last date</t>
         </is>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Answer key-Online Exam</t>
+          <t>Skip to main content</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr"/>
       <c r="D129" s="2" t="inlineStr"/>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/answerkey_onlineexams</t>
+          <t>https://www.keralapsc.gov.in/notifications#main-content</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="K129" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L129" s="2" t="inlineStr">
@@ -16323,14 +16323,14 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>Answer key-Online Exam</t>
+          <t>Skip to main content</t>
         </is>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Answer key-Online Exam</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -16342,7 +16342,7 @@
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/notifications</t>
+          <t>https://www.keralapsc.gov.in/answerkey_onlineexams</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -16380,7 +16380,7 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Answer key-Online Exam</t>
         </is>
       </c>
     </row>
@@ -16399,7 +16399,7 @@
       <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/status_of_advice</t>
+          <t>https://www.keralapsc.gov.in/status_of_advice</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -16456,7 +16456,7 @@
       <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/registration-thrown-out-candidates</t>
+          <t>https://www.keralapsc.gov.in/registration-thrown-out-candidates</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -16513,7 +16513,7 @@
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/index.php/general-conditions</t>
+          <t>https://www.keralapsc.gov.in/general-conditions</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">

--- a/jobs/government_jobs_tracker.xlsx
+++ b/jobs/government_jobs_tracker.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eligible Apply Now'!$A$1:$M$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Doubtful Manual Check'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avoid or Closed'!$A$1:$M$135</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Raw Matches'!$A$1:$M$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avoid or Closed'!$A$1:$M$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Raw Matches'!$A$1:$M$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sources'!$A$1:$D$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Profile'!$A$1:$B$10</definedName>
   </definedNames>
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M135"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1348,7 +1348,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Regular)-2025 Advt.No.-01/2026 (02-07-2026)</t>
+          <t>Press release and written result of the Recruitment of Forest Range Officer,Advt.No.-04/2024 (03-07-2026)</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1358,17 +1358,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_P.T_Result_01_26_dated_02_07_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_04_24_dated_03_07_2026.pdf</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1406,44 +1406,44 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Regular)-2025 Advt.No.-01/2026 (02-07-2026)</t>
+          <t>Press release and written result of the Recruitment of Forest Range Officer,Advt.No.-04/2024 (03-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Press release and written result of the Recruitment of Forest Range Officer,Advt.No.-04/2024 (03-07-2026)</t>
+          <t>Examination | Combined State/Upper Subordinate Services Examination | | A-1/E-1/2026 , 25/06/2026 | 25/06/2026 | 27/07/2026 | 27/07/2026 | 03/08/2026 | 25/06/2026 03/08/2026 | User</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_04_24_dated_03_07_2026.pdf</t>
+          <t>https://uppsc.up.nic.in/OuterPages/UserHelp.aspx?ID=114</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>UPPSC</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1461,54 +1461,54 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Press release and written result of the Recruitment of Forest Range Officer,Advt.No.-04/2024 (03-07-2026)</t>
+          <t>Examination | Combined State/Upper Subordinate Services Examination | | A-1/E-1/2026 , 25/06/2026 | 25/06/2026 | 27/07/2026 | 27/07/2026 | 03/08/2026 | 25/06/2026 03/08/2026 | User Instructions | View Advertisement | Apply</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Examination | Combined State/Upper Subordinate Services Examination | | A-1/E-1/2026 , 25/06/2026 | 25/06/2026 | 27/07/2026 | 27/07/2026 | 03/08/2026 | 25/06/2026 03/08/2026 | User</t>
+          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 (06-07-2026)</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/OuterPages/UserHelp.aspx?ID=114</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_and_P.T_Result_05_26_dated_06_07_2026.pdf</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>UPPSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1526,44 +1526,44 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Examination | Combined State/Upper Subordinate Services Examination | | A-1/E-1/2026 , 25/06/2026 | 25/06/2026 | 27/07/2026 | 27/07/2026 | 03/08/2026 | 25/06/2026 03/08/2026 | User Instructions | View Advertisement | Apply</t>
+          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 (06-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 (06-07-2026)</t>
+          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_P.T_Result_05_26_dated_06_07_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_07_07_2026.pdf</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -1601,19 +1601,19 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 (06-07-2026)</t>
+          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
+          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_07_07_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_03_24_dated_07_07_2026.pdf</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -1666,34 +1666,34 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
+          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
+          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_03_24_dated_07_07_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_15_23_dated_08_12_2025.pdf</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1731,34 +1731,34 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
+          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
+          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>08-12-2025</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>08-12-2025</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_15_23_dated_08_12_2025.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_09_05_2026.pdf</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
+          <t>Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -1796,34 +1796,34 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
+          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
+          <t>Press release regarding Jharkhand Combined Civil Services Examination, Advt.No.-01/2026, 05/2026 and 06/2026 (09-07-2026)</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>09-07-2026</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>09-07-2026</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_09_05_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_06_26_dated_09_07_2026.pdf</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched | Last date appears closed</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
+          <t>Press release regarding Jharkhand Combined Civil Services Examination, Advt.No.-01/2026, 05/2026 and 06/2026 (09-07-2026)</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0506603f0071/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2706,34 +2706,34 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/2026 | 2026-06-26</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2771,34 +2771,34 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-237201a5007a/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2836,34 +2836,34 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-02</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47bdf7690092/publicNotice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47ba32d3008f/publicNotice</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-09</t>
         </is>
       </c>
     </row>
@@ -8645,8 +8645,635 @@
         </is>
       </c>
     </row>
+    <row r="136" ht="30" customHeight="1">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Skip to Main Content</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr"/>
+      <c r="D136" s="2" t="inlineStr"/>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx#data</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>Skip to Main Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Vision &amp; Mission</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr"/>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=2UwI/bnoe0Bk6sAjqEVqwQ==</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>Vision &amp; Mission</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="30" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Commission &amp; Incumbency Chart</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=ZJj9IBSdU7Y1yw0WvPyFPw==</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Commission &amp; Incumbency Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="30" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Download Admission Certificate</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr"/>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl15','')</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Download Admission Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Advertisements</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr"/>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=MeNGKau42B9VX4Nn6oZfXA==</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Advertisements</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="30" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr"/>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=iQvy8ONZ1XeCyxFZaY2SfA==</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Download Admission Certificate</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr"/>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=VO/uz97buK3DBoFIVkTEOw==</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>Download Admission Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Transparency &amp; Objectivity</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr"/>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=jWDzPJrrf4pbXjUrVhA7Hg==</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>Transparency &amp; Objectivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Calendar</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr"/>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=N5n/48rKoj1sNGZtqat51w==</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Attestation &amp; Bio Data Form</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=M4ZLp2jMx/L7RLr5Gfi2Eg==</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>Attestation &amp; Bio Data Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Usage Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr"/>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=wmpmoV8VNcfB9LTvZnxjTQ==</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>Usage Terms &amp; Conditions</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M135"/>
+  <autoFilter ref="A1:M146"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8657,7 +9284,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -9372,7 +9999,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Regular)-2025 Advt.No.-01/2026 (02-07-2026)</t>
+          <t>Press release and written result of the Recruitment of Forest Range Officer,Advt.No.-04/2024 (03-07-2026)</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -9382,17 +10009,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>02-07-2026</t>
+          <t>03-07-2026</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_P.T_Result_01_26_dated_02_07_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_04_24_dated_03_07_2026.pdf</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -9430,44 +10057,44 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Regular)-2025 Advt.No.-01/2026 (02-07-2026)</t>
+          <t>Press release and written result of the Recruitment of Forest Range Officer,Advt.No.-04/2024 (03-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Press release and written result of the Recruitment of Forest Range Officer,Advt.No.-04/2024 (03-07-2026)</t>
+          <t>Examination | Combined State/Upper Subordinate Services Examination | | A-1/E-1/2026 , 25/06/2026 | 25/06/2026 | 27/07/2026 | 27/07/2026 | 03/08/2026 | 25/06/2026 03/08/2026 | User</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>03-07-2026</t>
+          <t>03/08/2026</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_04_24_dated_03_07_2026.pdf</t>
+          <t>https://uppsc.up.nic.in/OuterPages/UserHelp.aspx?ID=114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>UPPSC</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -9485,54 +10112,54 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Press release and written result of the Recruitment of Forest Range Officer,Advt.No.-04/2024 (03-07-2026)</t>
+          <t>Examination | Combined State/Upper Subordinate Services Examination | | A-1/E-1/2026 , 25/06/2026 | 25/06/2026 | 27/07/2026 | 27/07/2026 | 03/08/2026 | 25/06/2026 03/08/2026 | User Instructions | View Advertisement | Apply</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Examination | Combined State/Upper Subordinate Services Examination | | A-1/E-1/2026 , 25/06/2026 | 25/06/2026 | 27/07/2026 | 27/07/2026 | 03/08/2026 | 25/06/2026 03/08/2026 | User</t>
+          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 (06-07-2026)</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>03/08/2026</t>
+          <t>06-07-2026</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/OuterPages/UserHelp.aspx?ID=114</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_and_P.T_Result_05_26_dated_06_07_2026.pdf</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>UPPSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -9550,44 +10177,44 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Examination | Combined State/Upper Subordinate Services Examination | | A-1/E-1/2026 , 25/06/2026 | 25/06/2026 | 27/07/2026 | 27/07/2026 | 03/08/2026 | 25/06/2026 03/08/2026 | User Instructions | View Advertisement | Apply</t>
+          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 (06-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 (06-07-2026)</t>
+          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>06-07-2026</t>
+          <t>07-07-2026</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_P.T_Result_05_26_dated_06_07_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_07_07_2026.pdf</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -9615,7 +10242,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -9625,19 +10252,19 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Press release and P.T. result of the Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 (06-07-2026)</t>
+          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
+          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -9652,7 +10279,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_07_07_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_03_24_dated_07_07_2026.pdf</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -9667,7 +10294,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -9680,7 +10307,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -9690,34 +10317,34 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Combined Civil Services Main Examination Uploaded date:-07-07-2026</t>
+          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
+          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>07-07-2026</t>
+          <t>08-12-2025</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_and_Written_Result_03_24_dated_07_07_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_15_23_dated_08_12_2025.pdf</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -9732,7 +10359,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -9745,7 +10372,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
@@ -9755,34 +10382,34 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>Press release and written result of the Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024 (07-07-2026)</t>
+          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
+          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>08-12-2025</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>08-12-2025</t>
+          <t>09-05-2026</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_15_23_dated_08_12_2025.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_09_05_2026.pdf</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -9810,7 +10437,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: prosecution | Last date appears closed</t>
+          <t>Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -9820,34 +10447,34 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>Press Release regarding Recruitment of Deputy Director, Prosecution Advt.No.-15/2023 Uploaded date:-08-12-2025</t>
+          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
+          <t>Press release regarding Jharkhand Combined Civil Services Examination, Advt.No.-01/2026, 05/2026 and 06/2026 (09-07-2026)</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>09-07-2026</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>09-05-2026</t>
+          <t>09-07-2026</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/Press_Release_05_26_dated_09_05_2026.pdf</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_06_26_dated_09_07_2026.pdf</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9875,7 +10502,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched | Last date appears closed</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -9885,7 +10512,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>Press release and Instructions regarding Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026 uploaded date :09-05-2026</t>
+          <t>Press release regarding Jharkhand Combined Civil Services Examination, Advt.No.-01/2026, 05/2026 and 06/2026 (09-07-2026)</t>
         </is>
       </c>
     </row>
@@ -10672,7 +11299,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -10682,17 +11309,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0506603f0071/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -10730,34 +11357,34 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 01/2026, 02/2026 &amp; 04/2026 | 2026-06-26</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -10785,7 +11412,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -10795,34 +11422,34 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-237201a5007a/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -10850,7 +11477,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -10860,34 +11487,34 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-02</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47bdf7690092/publicNotice</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -10915,7 +11542,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -10925,34 +11552,34 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47ba32d3008f/publicNotice</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -10980,7 +11607,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
@@ -10990,7 +11617,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-09</t>
         </is>
       </c>
     </row>
@@ -16669,8 +17296,635 @@
         </is>
       </c>
     </row>
+    <row r="137" ht="30" customHeight="1">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Skip to Main Content</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr"/>
+      <c r="D137" s="2" t="inlineStr"/>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx#data</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>Skip to Main Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="30" customHeight="1">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Vision &amp; Mission</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr"/>
+      <c r="D138" s="2" t="inlineStr"/>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=2UwI/bnoe0Bk6sAjqEVqwQ==</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J138" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>Vision &amp; Mission</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="30" customHeight="1">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Commission &amp; Incumbency Chart</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr"/>
+      <c r="D139" s="2" t="inlineStr"/>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=ZJj9IBSdU7Y1yw0WvPyFPw==</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J139" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>Commission &amp; Incumbency Chart</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="30" customHeight="1">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Download Admission Certificate</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr"/>
+      <c r="D140" s="2" t="inlineStr"/>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl15','')</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>Download Admission Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="30" customHeight="1">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Advertisements</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr"/>
+      <c r="D141" s="2" t="inlineStr"/>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=MeNGKau42B9VX4Nn6oZfXA==</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>Advertisements</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="30" customHeight="1">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr"/>
+      <c r="D142" s="2" t="inlineStr"/>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=iQvy8ONZ1XeCyxFZaY2SfA==</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J142" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Download Admission Certificate</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr"/>
+      <c r="D143" s="2" t="inlineStr"/>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=VO/uz97buK3DBoFIVkTEOw==</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>Download Admission Certificate</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="30" customHeight="1">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Transparency &amp; Objectivity</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr"/>
+      <c r="D144" s="2" t="inlineStr"/>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=jWDzPJrrf4pbXjUrVhA7Hg==</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J144" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>Transparency &amp; Objectivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="30" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Calendar</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr"/>
+      <c r="D145" s="2" t="inlineStr"/>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=N5n/48rKoj1sNGZtqat51w==</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J145" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="30" customHeight="1">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Attestation &amp; Bio Data Form</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr"/>
+      <c r="D146" s="2" t="inlineStr"/>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=M4ZLp2jMx/L7RLr5Gfi2Eg==</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J146" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>Attestation &amp; Bio Data Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="30" customHeight="1">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Usage Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr"/>
+      <c r="D147" s="2" t="inlineStr"/>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=wmpmoV8VNcfB9LTvZnxjTQ==</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J147" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>Usage Terms &amp; Conditions</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M136"/>
+  <autoFilter ref="A1:M147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/jobs/government_jobs_tracker.xlsx
+++ b/jobs/government_jobs_tracker.xlsx
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2648,27 +2648,27 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
@@ -2706,34 +2706,34 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -2771,34 +2771,34 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47bdf7690092/publicNotice</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -2836,19 +2836,19 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2863,7 +2863,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47bdf7690092/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47ba32d3008f/publicNotice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2901,14 +2901,14 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
+          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2918,17 +2918,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47ba32d3008f/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-4c3834130095/publicNotice</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-09</t>
+          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-10</t>
         </is>
       </c>
     </row>
@@ -8831,7 +8831,7 @@
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl15','')</t>
+          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl29','')</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -10459,7 +10459,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -11299,27 +11299,27 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 20</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-23d707fe007d/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -11347,7 +11347,7 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
@@ -11357,34 +11357,34 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENT NOS. 13/2024, 02/2026 &amp; 04/2026 | 2026-07-02</t>
+          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2d7fabd90086/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -11412,7 +11412,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
@@ -11422,34 +11422,34 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE REGARDING DISPLAY OF OMR ANSWER SHEETS OF THE COMMON ELIGIBILITY TEST (CET)-2025 (GROUP-C) WRITTEN EXAMINATION IN CANDIDATE LOGIN OF ALL APPEARED CANDIDATES | 2026-07-04</t>
+          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-3cc194ce008c/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47bdf7690092/publicNotice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai, mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -11487,19 +11487,19 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE REGARDING CONSIDERING CLOSING DATE OF SUBMISSION OF APPLICATION FORM FOR THE POST OF GROUP-D AGAINST ADVERTISEMENT NO. 05/2026. | 2026-07-07</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -11514,7 +11514,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47bdf7690092/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47ba32d3008f/publicNotice</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -11542,7 +11542,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -11552,14 +11552,14 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-09</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01</t>
+          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47ba32d3008f/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-4c3834130095/publicNotice</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -11617,7 +11617,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR MALE CONSTABLE (GD) AND MALE CONSTABLE (GOVERNMENT RAILWAY POLICE) AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 01 AND 03 OF POLICE DEPARTMENT, HARYANA. | 2026-07-09</t>
+          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-10</t>
         </is>
       </c>
     </row>
@@ -17482,7 +17482,7 @@
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl15','')</t>
+          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl29','')</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">

--- a/jobs/government_jobs_tracker.xlsx
+++ b/jobs/government_jobs_tracker.xlsx
@@ -2913,7 +2913,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -11564,7 +11564,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -11607,7 +11607,7 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">

--- a/jobs/government_jobs_tracker.xlsx
+++ b/jobs/government_jobs_tracker.xlsx
@@ -8831,7 +8831,7 @@
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl29','')</t>
+          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl43','')</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -17482,7 +17482,7 @@
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl29','')</t>
+          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl43','')</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">

--- a/jobs/government_jobs_tracker.xlsx
+++ b/jobs/government_jobs_tracker.xlsx
@@ -17,8 +17,8 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Eligible Apply Now'!$A$1:$M$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Doubtful Manual Check'!$A$1:$M$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avoid or Closed'!$A$1:$M$163</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Raw Matches'!$A$1:$M$164</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Avoid or Closed'!$A$1:$M$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Raw Matches'!$A$1:$M$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Sources'!$A$1:$D$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Profile'!$A$1:$B$10</definedName>
   </definedNames>
@@ -690,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M163"/>
+  <dimension ref="A1:M165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2583,7 +2583,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
+          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47bdf7690092/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-4c3834130095/publicNotice</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2641,14 +2641,14 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
+          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 | 2026-07-14</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2658,17 +2658,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-4c3834130095/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-606f6f7a0098/publicNotice</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2706,14 +2706,14 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-10</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 | 2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 | 2026-07-14</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF FEMALE CONSTABLE AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 02 OF POLICE DEPARTMENT, HARYANA. | 2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2723,17 +2723,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-606f6f7a0098/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-6b93802b009e/publicNotice</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -2771,14 +2771,14 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 | 2026-07-14</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF FEMALE CONSTABLE AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 02 OF POLICE DEPARTMENT, HARYANA. | 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF FEMALE CONSTABLE AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 02 OF POLICE DEPARTMENT, HARYANA. | 2026</t>
+          <t xml:space="preserve">RE-SCHEDULE NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF </t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -2798,7 +2798,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-6b93802b009e/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-6a467550009b/publicNotice</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2836,34 +2836,34 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF FEMALE CONSTABLE AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 02 OF POLICE DEPARTMENT, HARYANA. | 2026-07-16</t>
+          <t>RE-SCHEDULE NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RE-SCHEDULE NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF </t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE VARIOUS POSTS AGAINST ADVT. NOS. 13/2024, 01/2026 and 06/2026. | 2026-07-22</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-6a467550009b/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9f7f-1923-819f-8af999770001/publicNotice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -2891,7 +2891,7 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
@@ -2901,44 +2901,44 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>RE-SCHEDULE NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-16</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE VARIOUS POSTS AGAINST ADVT. NOS. 13/2024, 01/2026 and 06/2026. | 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
+          <t>Press release regarding recruitment of Jharkhand Combined Civil Services Main (written) Examination-2025 Advt.No.-01/2026 and Examination Calendar-2026 (22-07-2026)</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>22-07-2026</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>26-02-2026</t>
+          <t>22-07-2026</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_01_26_dated_22_07_2026.pdf</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -2956,54 +2956,54 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
+          <t>Press release regarding recruitment of Jharkhand Combined Civil Services Main (written) Examination-2025 Advt.No.-01/2026 and Examination Calendar-2026 (22-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>The Jharkhand Examination (Measures Control and Prevention of Unfair Means in Recruitment) Act, 2023 (Jharkhand Act, 15,2023) uploaded date :29-11-2023</t>
+          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>29-11-2023</t>
+          <t>28-01-2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>29-11-2023</t>
+          <t>26-02-2026</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/jharkhand%20gazette_29_11_2023.pdf</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -3021,54 +3021,54 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>The Jharkhand Examination (Measures Control and Prevention of Unfair Means in Recruitment) Act, 2023 (Jharkhand Act, 15,2023) uploaded date :29-11-2023</t>
+          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 02-10-2023 11:30 Hrs Last date for Submission of applications: 31-10-2023 17:30 Hrs</t>
+          <t>The Jharkhand Examination (Measures Control and Prevention of Unfair Means in Recruitment) Act, 2023 (Jharkhand Act, 15,2023) uploaded date :29-11-2023</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>02-10-2023</t>
+          <t>29-11-2023</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>31-10-2023</t>
+          <t>29-11-2023</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/data/jharkhand%20gazette_29_11_2023.pdf</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -3086,46 +3086,54 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 02-10-2023 11:30 Hrs Last date for Submission of applications: 31-10-2023 17:30 Hrs</t>
+          <t>The Jharkhand Examination (Measures Control and Prevention of Unfair Means in Recruitment) Act, 2023 (Jharkhand Act, 15,2023) uploaded date :29-11-2023</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Please click here to read the Frequently Asked Question about Recruitment portal.</t>
+          <t>Start date for Submission of applications: 02-10-2023 11:30 Hrs Last date for Submission of applications: 31-10-2023 17:30 Hrs</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr"/>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>02-10-2023</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>31-10-2023</t>
+        </is>
+      </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://recruitment.rajasthan.gov.in/frequentlyaskedquestions</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>State Recruitment Portal</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3143,24 +3151,24 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://recruitment.rajasthan.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Please click here to read the Frequently Asked Question about Recruitment portal.</t>
+          <t>Start date for Submission of applications: 02-10-2023 11:30 Hrs Last date for Submission of applications: 31-10-2023 17:30 Hrs</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>recruitmenthelpdesk@rajasthan.gov.in</t>
+          <t>Please click here to read the Frequently Asked Question about Recruitment portal.</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -3172,7 +3180,7 @@
       <c r="D40" s="2" t="inlineStr"/>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>mailto:recruitmenthelpdesk@rajasthan.gov.in</t>
+          <t>https://recruitment.rajasthan.gov.in/frequentlyaskedquestions</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -3210,36 +3218,36 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>recruitmenthelpdesk@rajasthan.gov.in</t>
+          <t>Please click here to read the Frequently Asked Question about Recruitment portal.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>S.No | Advertisement Number | Advertisement Name | Registration Start Date | Registration End Date | Application Last Date | Payment Last Day | View Document | Link</t>
+          <t>recruitmenthelpdesk@rajasthan.gov.in</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr"/>
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>mailto:recruitmenthelpdesk@rajasthan.gov.in</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>BTSC</t>
+          <t>State Recruitment Portal</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3257,24 +3265,24 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>https://recruitment.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>S.No | Advertisement Number | Advertisement Name | Registration Start Date | Registration End Date | Application Last Date | Payment Last Day | View Document | Link</t>
+          <t>recruitmenthelpdesk@rajasthan.gov.in</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Advertisement</t>
+          <t>S.No | Advertisement Number | Advertisement Name | Registration Start Date | Registration End Date | Application Last Date | Payment Last Day | View Document | Link</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -3286,7 +3294,7 @@
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/24_2026.pdf  </t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -3324,7 +3332,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>Advertisement</t>
+          <t>S.No | Advertisement Number | Advertisement Name | Registration Start Date | Registration End Date | Application Last Date | Payment Last Day | View Document | Link</t>
         </is>
       </c>
     </row>
@@ -3343,7 +3351,7 @@
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/23_2026_0.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/24_2026.pdf  </t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -3400,7 +3408,7 @@
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/22_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/23_2026_0.pdf  </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -3457,7 +3465,7 @@
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/21_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/22_2026.pdf  </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -3514,7 +3522,7 @@
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/20_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/21_2026.pdf  </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -3571,7 +3579,7 @@
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/19_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/20_2026.pdf  </t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -3628,7 +3636,7 @@
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/18_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/19_2026.pdf  </t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -3685,7 +3693,7 @@
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/17_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/18_2026.pdf  </t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -3742,7 +3750,7 @@
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/16_%202026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/17_2026.pdf  </t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -3799,7 +3807,7 @@
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/15_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/16_%202026.pdf  </t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -3844,19 +3852,19 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Advertisement</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment#main-content</t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/15_2026.pdf  </t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -3884,7 +3892,7 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
@@ -3894,14 +3902,14 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Advertisement</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Skip to Main Content</t>
+          <t>Skip to main content</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -3913,7 +3921,7 @@
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment#wrapper</t>
+          <t>https://btsc.bihar.gov.in/recruitment#main-content</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -3951,26 +3959,26 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Skip to Main Content</t>
+          <t>Skip to main content</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Bihar Technical Service Commission</t>
+          <t>Skip to Main Content</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr"/>
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/</t>
+          <t>https://btsc.bihar.gov.in/recruitment#wrapper</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -3985,7 +3993,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Technical/IT</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I54" s="2" t="n">
@@ -3998,7 +4006,7 @@
       </c>
       <c r="K54" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
@@ -4008,26 +4016,26 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Bihar Technical Service Commission</t>
+          <t>Skip to Main Content</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Admit Card/Call Letter</t>
+          <t>Bihar Technical Service Commission</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/admit-card</t>
+          <t>https://btsc.bihar.gov.in/</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -4042,7 +4050,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Technical/IT</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
@@ -4055,7 +4063,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -4065,26 +4073,26 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Admit Card/Call Letter</t>
+          <t>Bihar Technical Service Commission</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Admit Card/Call Letter</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/website-policies</t>
+          <t>https://btsc.bihar.gov.in/admit-card</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -4112,7 +4120,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -4122,26 +4130,26 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Admit Card/Call Letter</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Website Policies</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/disclaimer</t>
+          <t>https://btsc.bihar.gov.in/website-policies</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -4169,7 +4177,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -4179,36 +4187,36 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Website Policies</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconcil</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://btsc.bihar.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>UPPSC</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -4226,36 +4234,36 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconciliation | Modification Start Date Last Date | | |</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Notification Based On OTR</t>
+          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconcil</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>javascript:void();</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -4283,7 +4291,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -4293,14 +4301,14 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Notification Based On OTR</t>
+          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconciliation | Modification Start Date Last Date | | |</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>View Advertisement</t>
+          <t>Notification Based On OTR</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -4312,7 +4320,7 @@
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/OuterPages/View_Advertisement.aspx?ID=114&amp;flag=E</t>
+          <t>javascript:void();</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -4350,26 +4358,26 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>View Advertisement</t>
+          <t>Notification Based On OTR</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>{{'SiteMap_HM' | translate }}</t>
+          <t>View Advertisement</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr"/>
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/FooterPages/SiteMap.aspx</t>
+          <t>https://uppsc.up.nic.in/OuterPages/View_Advertisement.aspx?ID=114&amp;flag=E</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -4397,7 +4405,7 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
@@ -4407,36 +4415,36 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>{{'SiteMap_HM' | translate }}</t>
+          <t>View Advertisement</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>{{'SiteMap_HM' | translate }}</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb-vacancies#main-content</t>
+          <t>https://uppsc.up.nic.in/FooterPages/SiteMap.aspx</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>DSSSB</t>
+          <t>UPPSC</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
@@ -4454,36 +4462,36 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb-vacancies</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>{{'SiteMap_HM' | translate }}</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Skip to main content</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/citizen-charter</t>
+          <t>https://dsssb.delhi.gov.in/dsssb-vacancies#main-content</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -4511,7 +4519,7 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
@@ -4521,26 +4529,26 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Skip to main content</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>List of Chairpersons</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/list-chairpersons</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/citizen-charter</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -4568,7 +4576,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -4578,26 +4586,26 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>List of Chairpersons</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Archived Vacancies</t>
+          <t>List of Chairpersons</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/archived-vacancies</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/list-chairpersons</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -4625,7 +4633,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -4635,26 +4643,26 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Archived Vacancies</t>
+          <t>List of Chairpersons</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Recruitment Rules of Combined Exam</t>
+          <t>Archived Vacancies</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/recruitment-rules-combined-exam</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/archived-vacancies</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -4682,7 +4690,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -4692,26 +4700,26 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Recruitment Rules of Combined Exam</t>
+          <t>Archived Vacancies</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2018</t>
+          <t>Recruitment Rules of Combined Exam</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2018</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/recruitment-rules-combined-exam</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -4739,7 +4747,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -4749,14 +4757,14 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2018</t>
+          <t>Recruitment Rules of Combined Exam</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2019</t>
+          <t>Question Bank Online Exam 2018</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -4768,7 +4776,7 @@
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2019</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2018</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -4806,14 +4814,14 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2019</t>
+          <t>Question Bank Online Exam 2018</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2021</t>
+          <t>Question Bank Online Exam 2019</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -4825,7 +4833,7 @@
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/dsssb-previous-year-paper-2021</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2019</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -4863,14 +4871,14 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2021</t>
+          <t>Question Bank Online Exam 2019</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2022</t>
+          <t>Question Bank Online Exam 2021</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4882,7 +4890,7 @@
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2022</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/dsssb-previous-year-paper-2021</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -4920,14 +4928,14 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2022</t>
+          <t>Question Bank Online Exam 2021</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2023</t>
+          <t>Question Bank Online Exam 2022</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -4939,7 +4947,7 @@
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2023</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2022</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -4977,14 +4985,14 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2023</t>
+          <t>Question Bank Online Exam 2022</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2024</t>
+          <t>Question Bank Online Exam 2023</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -4996,7 +5004,7 @@
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2024</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2023</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -5034,14 +5042,14 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2024</t>
+          <t>Question Bank Online Exam 2023</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2025</t>
+          <t>Question Bank Online Exam 2024</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -5053,7 +5061,7 @@
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2025</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2024</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -5091,26 +5099,26 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2025</t>
+          <t>Question Bank Online Exam 2024</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Staff Selection Commission</t>
+          <t>Question Bank Online Exam 2025</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr"/>
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://ssc.nic.in/</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2025</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -5138,7 +5146,7 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
@@ -5148,14 +5156,14 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Staff Selection Commission</t>
+          <t>Question Bank Online Exam 2025</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Union Public Service Commission</t>
+          <t>Staff Selection Commission</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -5167,7 +5175,7 @@
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://upsc.gov.in/index.php</t>
+          <t>https://ssc.nic.in/</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -5205,26 +5213,26 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Union Public Service Commission</t>
+          <t>Staff Selection Commission</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Department of Personnel and Training</t>
+          <t>Union Public Service Commission</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr"/>
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://upsc.gov.in/index.php</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -5252,7 +5260,7 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
@@ -5262,26 +5270,26 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Department of Personnel and Training</t>
+          <t>Union Public Service Commission</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Recruitments</t>
+          <t>Department of Personnel and Training</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/recruitment</t>
+          <t>https://dopt.gov.in/</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -5309,7 +5317,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -5319,26 +5327,26 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Recruitments</t>
+          <t>Department of Personnel and Training</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Recruitments</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/website-policies</t>
+          <t>https://dsssb.delhi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -5366,7 +5374,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -5376,14 +5384,14 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Recruitments</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Feedback (Want to give any suggestion for improvement on our website?)</t>
+          <t>Website Policies</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -5395,7 +5403,7 @@
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/feedback</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/website-policies</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -5433,26 +5441,26 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Feedback (Want to give any suggestion for improvement on our website?)</t>
+          <t>Website Policies</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Vigilance Complaint Information Management System (VCIMS)</t>
+          <t>Feedback (Want to give any suggestion for improvement on our website?)</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr"/>
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://vcims.delhi.gov.in/</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/feedback</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -5480,7 +5488,7 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
@@ -5490,36 +5498,36 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Vigilance Complaint Information Management System (VCIMS)</t>
+          <t>Feedback (Want to give any suggestion for improvement on our website?)</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>Vigilance Complaint Information Management System (VCIMS)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
+          <t>https://vcims.delhi.gov.in/</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>DSSSB</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -5537,24 +5545,24 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://dsssb.delhi.gov.in/dsssb-vacancies</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>Vigilance Complaint Information Management System (VCIMS)</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -5566,7 +5574,7 @@
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -5581,7 +5589,7 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I82" s="2" t="n">
@@ -5604,14 +5612,14 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -5623,7 +5631,7 @@
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
+          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -5638,7 +5646,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -5661,14 +5669,14 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -5680,7 +5688,7 @@
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -5718,14 +5726,14 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -5737,7 +5745,7 @@
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -5752,7 +5760,7 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I85" s="2" t="n">
@@ -5775,14 +5783,14 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -5794,7 +5802,7 @@
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
+          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -5809,7 +5817,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
@@ -5832,36 +5840,36 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
+          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr"/>
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>HSSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
@@ -5879,36 +5887,36 @@
       </c>
       <c r="K87" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
+          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>Apply for CET Group D-05/2026</t>
+          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://onetimeregn.haryana.gov.in/hssc</t>
+          <t>https://hssc.gov.in</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
@@ -5936,7 +5944,7 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
@@ -5946,26 +5954,26 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Apply for CET Group D-05/2026</t>
+          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Apply for CET Group D-05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/commission</t>
+          <t>https://onetimeregn.haryana.gov.in/hssc</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -5993,7 +6001,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
@@ -6003,83 +6011,83 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Apply for CET Group D-05/2026</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Commission</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
+          <t>https://hssc.gov.in/commission</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>HSSC</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
           <t>https://hssc.gov.in/</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>HSSC</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>General/Other</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>Avoid or Closed</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
-        <is>
-          <t>https://hssc.gov.in/</t>
-        </is>
-      </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Commission</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/advertisement</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
@@ -6107,7 +6115,7 @@
       </c>
       <c r="K91" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr">
@@ -6117,26 +6125,26 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Recruitment</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Advertisements</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/citizenCharter</t>
+          <t>https://hssc.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -6164,7 +6172,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -6174,26 +6182,26 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Advertisements</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/notifications</t>
+          <t>https://hssc.gov.in/citizenCharter</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -6221,7 +6229,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -6231,14 +6239,14 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Apply Online</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -6250,7 +6258,7 @@
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/applyOnline</t>
+          <t>https://hssc.gov.in/notifications</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -6288,26 +6296,26 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Apply Online</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
+          <t>Apply Online</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr"/>
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-37163ea80089/result</t>
+          <t>https://hssc.gov.in/applyOnline</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -6335,7 +6343,7 @@
       </c>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr">
@@ -6345,14 +6353,14 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
+          <t>Apply Online</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
+          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -6364,7 +6372,7 @@
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2b35286b0083/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-37163ea80089/result</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -6402,14 +6410,14 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
+          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -6421,7 +6429,7 @@
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-14153adb0074/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2b35286b0083/result</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -6459,26 +6467,26 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social </t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr"/>
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0315bb59006e/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-14153adb0074/result</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -6506,7 +6514,7 @@
       </c>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr">
@@ -6516,26 +6524,26 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social Studies (MWT) against Advt. No. 02/2023 and for the posts of TGT Punjabi (ROH) against Advt. No. 04/2023</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
+          <t xml:space="preserve">Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social </t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0275db17006b/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0315bb59006e/result</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -6563,7 +6571,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -6573,14 +6581,14 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
+          <t>Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social Studies (MWT) against Advt. No. 02/2023 and for the posts of TGT Punjabi (ROH) against Advt. No. 04/2023</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -6592,7 +6600,7 @@
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/termsConditions</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0275db17006b/result</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -6630,14 +6638,14 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Statement</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -6649,7 +6657,7 @@
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/accessibilityStatement</t>
+          <t>https://hssc.gov.in/termsConditions</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -6687,26 +6695,26 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Statement</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Accessibility Statement</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr"/>
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/disclaimer</t>
+          <t>https://hssc.gov.in/accessibilityStatement</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -6734,7 +6742,7 @@
       </c>
       <c r="K102" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L102" s="2" t="inlineStr">
@@ -6744,14 +6752,14 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Accessibility Statement</t>
         </is>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Go to main content</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -6763,17 +6771,17 @@
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/#container</t>
+          <t>https://hssc.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>HSSC</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
@@ -6796,31 +6804,31 @@
       </c>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>Go to main content</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>Go to main content</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr"/>
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/university_constituent.php</t>
+          <t>https://www.jpsc.gov.in/#container</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
@@ -6848,7 +6856,7 @@
       </c>
       <c r="K104" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L104" s="2" t="inlineStr">
@@ -6858,14 +6866,14 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>Go to main content</t>
         </is>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -6877,7 +6885,7 @@
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/affilated_religious.php</t>
+          <t>https://www.jpsc.gov.in/university_constituent.php</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -6915,14 +6923,14 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -6934,7 +6942,7 @@
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/carrer_uni.php</t>
+          <t>https://www.jpsc.gov.in/affilated_religious.php</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -6972,14 +6980,14 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -6991,7 +6999,7 @@
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/carrer_aff.php</t>
+          <t>https://www.jpsc.gov.in/carrer_uni.php</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -7029,14 +7037,14 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>Merit Promotion Scheme</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -7048,7 +7056,7 @@
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/merit_promotion_scheme.php</t>
+          <t>https://www.jpsc.gov.in/carrer_aff.php</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -7086,26 +7094,26 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Merit Promotion Scheme</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Online Application Form (OAS)</t>
+          <t>Merit Promotion Scheme</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr"/>
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/FAQ.pdf</t>
+          <t>https://www.jpsc.gov.in/merit_promotion_scheme.php</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -7133,7 +7141,7 @@
       </c>
       <c r="K109" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L109" s="2" t="inlineStr">
@@ -7143,14 +7151,14 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Online Application Form (OAS)</t>
+          <t>Merit Promotion Scheme</t>
         </is>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Online Application</t>
+          <t>Online Application Form (OAS)</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -7162,7 +7170,7 @@
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/?click=yes</t>
+          <t>https://www.jpsc.gov.in/data/FAQ.pdf</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -7200,26 +7208,26 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Online Application</t>
+          <t>Online Application Form (OAS)</t>
         </is>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>List of Recognised University/Institution</t>
+          <t>Online Application</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr"/>
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/list_uni.php</t>
+          <t>https://www.jpsc.gov.in/?click=yes</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -7247,7 +7255,7 @@
       </c>
       <c r="K111" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L111" s="2" t="inlineStr">
@@ -7257,14 +7265,14 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>List of Recognised University/Institution</t>
+          <t>Online Application</t>
         </is>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
+          <t>List of Recognised University/Institution</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -7276,7 +7284,7 @@
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13044</t>
+          <t>https://www.jpsc.gov.in/list_uni.php</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -7314,14 +7322,14 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
+          <t>List of Recognised University/Institution</t>
         </is>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -7333,7 +7341,7 @@
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13043</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13044</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -7371,14 +7379,14 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
         </is>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -7390,7 +7398,7 @@
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13039</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13043</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -7428,14 +7436,14 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
         </is>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -7447,7 +7455,7 @@
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13038</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13039</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -7485,14 +7493,14 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
+          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -7504,7 +7512,7 @@
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13035</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13038</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -7519,7 +7527,7 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
@@ -7542,14 +7550,14 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
+          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
         </is>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
+          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -7561,7 +7569,7 @@
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13034</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13035</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -7576,7 +7584,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
@@ -7599,14 +7607,14 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
+          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
         </is>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Director Advt.No.-07/2025</t>
+          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -7618,7 +7626,7 @@
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13033</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13034</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -7656,14 +7664,14 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Director Advt.No.-07/2025</t>
+          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
         </is>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
+          <t>Recruitment of Director Advt.No.-07/2025</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -7675,7 +7683,7 @@
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13032</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13033</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -7713,14 +7721,14 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
+          <t>Recruitment of Director Advt.No.-07/2025</t>
         </is>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
+          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -7732,7 +7740,7 @@
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13031</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13032</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -7770,14 +7778,14 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
+          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
         </is>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
+          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -7789,7 +7797,7 @@
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13030</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13031</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -7804,7 +7812,7 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I121" s="2" t="n">
@@ -7827,14 +7835,14 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
+          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
         </is>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -7846,7 +7854,7 @@
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13029</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13030</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -7884,14 +7892,14 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
         </is>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -7903,7 +7911,7 @@
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13028</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13029</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -7918,7 +7926,7 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I123" s="2" t="n">
@@ -7941,14 +7949,14 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
+          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -7960,7 +7968,7 @@
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13026</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13028</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -7998,14 +8006,14 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
+          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
+          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -8017,7 +8025,7 @@
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13025</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13026</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -8055,14 +8063,14 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
+          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
+          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -8074,7 +8082,7 @@
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13024</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13025</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -8089,7 +8097,7 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I126" s="2" t="n">
@@ -8112,14 +8120,14 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
+          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
         </is>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
+          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -8131,7 +8139,7 @@
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13021</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13024</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -8146,7 +8154,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
@@ -8169,14 +8177,14 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
+          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
         </is>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
+          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -8188,7 +8196,7 @@
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13020</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13021</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -8203,7 +8211,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
@@ -8226,14 +8234,14 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
+          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
         </is>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
+          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -8245,7 +8253,7 @@
       <c r="D129" s="2" t="inlineStr"/>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=140</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13020</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -8260,7 +8268,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
@@ -8283,14 +8291,14 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
+          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
         </is>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -8302,7 +8310,7 @@
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=134</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=140</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -8340,14 +8348,14 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
         </is>
       </c>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -8359,7 +8367,7 @@
       <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=133</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=134</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -8397,26 +8405,26 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
         </is>
       </c>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
+          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr"/>
       <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=120</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=133</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -8431,7 +8439,7 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
@@ -8444,7 +8452,7 @@
       </c>
       <c r="K132" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L132" s="2" t="inlineStr">
@@ -8454,14 +8462,14 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
+          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
         </is>
       </c>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
+          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -8473,7 +8481,7 @@
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=119</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=120</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -8511,14 +8519,14 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
+          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
         </is>
       </c>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
+          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -8530,7 +8538,7 @@
       <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=118</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=119</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -8568,26 +8576,26 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
+          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
         </is>
       </c>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
+          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr"/>
       <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=82</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=118</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -8615,7 +8623,7 @@
       </c>
       <c r="K135" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
         </is>
       </c>
       <c r="L135" s="2" t="inlineStr">
@@ -8625,26 +8633,26 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
+          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
         </is>
       </c>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
+          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr"/>
       <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=66</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=82</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -8659,7 +8667,7 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I136" s="2" t="n">
@@ -8672,7 +8680,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -8682,26 +8690,26 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
+          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
         </is>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
+          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr"/>
       <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=62</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=66</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -8729,7 +8737,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
@@ -8739,14 +8747,14 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
+          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
         </is>
       </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
+          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -8758,7 +8766,7 @@
       <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=61</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=62</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -8773,7 +8781,7 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I138" s="2" t="n">
@@ -8796,26 +8804,26 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
+          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
         </is>
       </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
+          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr"/>
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=51</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=61</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -8830,7 +8838,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
@@ -8843,7 +8851,7 @@
       </c>
       <c r="K139" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
         </is>
       </c>
       <c r="L139" s="2" t="inlineStr">
@@ -8853,26 +8861,26 @@
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
+          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
         </is>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
+          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr"/>
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=40</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=51</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -8900,7 +8908,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -8910,14 +8918,14 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
+          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
         </is>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
+          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -8929,7 +8937,7 @@
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=39</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=40</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -8967,26 +8975,26 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
+          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
         </is>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Email Login</t>
+          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr"/>
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in:2096/</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=39</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -9001,7 +9009,7 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I142" s="2" t="n">
@@ -9014,7 +9022,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L142" s="2" t="inlineStr">
@@ -9024,36 +9032,36 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>Email Login</t>
+          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
         </is>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Title | Category Number | Last date</t>
+          <t>Email Login</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications</t>
+          <t>https://www.jpsc.gov.in:2096/</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G143" s="2" t="inlineStr">
         <is>
-          <t>Kerala PSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H143" s="2" t="inlineStr">
@@ -9071,36 +9079,36 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>Title | Category Number | Last date</t>
+          <t>Email Login</t>
         </is>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Title | Category Number | Last date</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="2" t="inlineStr"/>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications#main-content</t>
+          <t>https://www.keralapsc.gov.in/notifications</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
@@ -9128,7 +9136,7 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
@@ -9138,26 +9146,26 @@
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Title | Category Number | Last date</t>
         </is>
       </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Answer key-Online Exam</t>
+          <t>Skip to main content</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr"/>
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/answerkey_onlineexams</t>
+          <t>https://www.keralapsc.gov.in/notifications#main-content</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -9185,7 +9193,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
@@ -9195,26 +9203,26 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>Answer key-Online Exam</t>
+          <t>Skip to main content</t>
         </is>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Details of Advice</t>
+          <t>Answer key-Online Exam</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr"/>
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/status_of_advice</t>
+          <t>https://www.keralapsc.gov.in/index.php/answerkey_onlineexams</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -9242,7 +9250,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -9252,14 +9260,14 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>Details of Advice</t>
+          <t>Answer key-Online Exam</t>
         </is>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Candidates Registration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -9271,7 +9279,7 @@
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/registration-thrown-out-candidates</t>
+          <t>https://www.keralapsc.gov.in/index.php/notifications</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -9309,26 +9317,26 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>Candidates Registration</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>General Conditions</t>
+          <t>Details of Advice</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr"/>
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/general-conditions</t>
+          <t>https://www.keralapsc.gov.in/index.php/status_of_advice</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -9356,7 +9364,7 @@
       </c>
       <c r="K148" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L148" s="2" t="inlineStr">
@@ -9366,26 +9374,26 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>General Conditions</t>
+          <t>Details of Advice</t>
         </is>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>Terms and Condition</t>
+          <t>Candidates Registration</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr"/>
       <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/terms-and-condition</t>
+          <t>https://www.keralapsc.gov.in/index.php/registration-thrown-out-candidates</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -9413,7 +9421,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -9423,26 +9431,26 @@
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>Terms and Condition</t>
+          <t>Candidates Registration</t>
         </is>
       </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>General Conditions</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr"/>
       <c r="D150" s="2" t="inlineStr"/>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/disclaimer</t>
+          <t>https://www.keralapsc.gov.in/index.php/general-conditions</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -9470,7 +9478,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -9480,26 +9488,26 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>General Conditions</t>
         </is>
       </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Digital Personal Data Protection Policy/Privacy Policy</t>
+          <t>Terms and Condition</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , data | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr"/>
       <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/privacy-policy</t>
+          <t>https://www.keralapsc.gov.in/terms-and-condition</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -9527,7 +9535,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , data | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -9537,26 +9545,26 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>Digital Personal Data Protection Policy/Privacy Policy</t>
+          <t>Terms and Condition</t>
         </is>
       </c>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Visit Old Website</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr"/>
       <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/old-website-temporarily-shutdown</t>
+          <t>https://www.keralapsc.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -9584,7 +9592,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -9594,36 +9602,36 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>Visit Old Website</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Skip to Main Content</t>
+          <t>Digital Personal Data Protection Policy/Privacy Policy</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , data | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr"/>
       <c r="D153" s="2" t="inlineStr"/>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx#data</t>
+          <t>https://www.keralapsc.gov.in/privacy-policy</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="G153" s="2" t="inlineStr">
         <is>
-          <t>OPSC</t>
+          <t>Kerala PSC</t>
         </is>
       </c>
       <c r="H153" s="2" t="inlineStr">
@@ -9641,46 +9649,46 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , data | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+          <t>https://www.keralapsc.gov.in/notifications</t>
         </is>
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>Skip to Main Content</t>
+          <t>Digital Personal Data Protection Policy/Privacy Policy</t>
         </is>
       </c>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Vision &amp; Mission</t>
+          <t>Visit Old Website</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr"/>
       <c r="D154" s="2" t="inlineStr"/>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=2UwI/bnoe0Bk6sAjqEVqwQ==</t>
+          <t>https://www.keralapsc.gov.in/old-website-temporarily-shutdown</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>OPSC</t>
+          <t>Kerala PSC</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -9698,36 +9706,36 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+          <t>https://www.keralapsc.gov.in/notifications</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>Vision &amp; Mission</t>
+          <t>Visit Old Website</t>
         </is>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Commission &amp; Incumbency Chart</t>
+          <t>Skip to Main Content</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr"/>
       <c r="D155" s="2" t="inlineStr"/>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=ZJj9IBSdU7Y1yw0WvPyFPw==</t>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx#data</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
@@ -9755,7 +9763,7 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
@@ -9765,26 +9773,26 @@
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>Commission &amp; Incumbency Chart</t>
+          <t>Skip to Main Content</t>
         </is>
       </c>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Submit Objection / Suggestion</t>
+          <t>Vision &amp; Mission</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr"/>
       <c r="D156" s="2" t="inlineStr"/>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl59','')</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=2UwI/bnoe0Bk6sAjqEVqwQ==</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -9812,7 +9820,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -9822,26 +9830,26 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>Submit Objection / Suggestion</t>
+          <t>Vision &amp; Mission</t>
         </is>
       </c>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Commission &amp; Incumbency Chart</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr"/>
       <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=MeNGKau42B9VX4Nn6oZfXA==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=ZJj9IBSdU7Y1yw0WvPyFPw==</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -9869,7 +9877,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
@@ -9879,26 +9887,26 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Commission &amp; Incumbency Chart</t>
         </is>
       </c>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Submit Objection / Suggestion</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr"/>
       <c r="D158" s="2" t="inlineStr"/>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=iQvy8ONZ1XeCyxFZaY2SfA==</t>
+          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl59','')</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -9926,7 +9934,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -9936,26 +9944,26 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Submit Objection / Suggestion</t>
         </is>
       </c>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Download Admission Certificate</t>
+          <t>Advertisements</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr"/>
       <c r="D159" s="2" t="inlineStr"/>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=VO/uz97buK3DBoFIVkTEOw==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=MeNGKau42B9VX4Nn6oZfXA==</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -9983,7 +9991,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
@@ -9993,26 +10001,26 @@
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>Download Admission Certificate</t>
+          <t>Advertisements</t>
         </is>
       </c>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Transparency &amp; Objectivity</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr"/>
       <c r="D160" s="2" t="inlineStr"/>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=jWDzPJrrf4pbXjUrVhA7Hg==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=iQvy8ONZ1XeCyxFZaY2SfA==</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -10040,7 +10048,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -10050,26 +10058,26 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>Transparency &amp; Objectivity</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Recruitment Calendar</t>
+          <t>Download Admission Certificate</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr"/>
       <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=N5n/48rKoj1sNGZtqat51w==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=VO/uz97buK3DBoFIVkTEOw==</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -10097,7 +10105,7 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L161" s="2" t="inlineStr">
@@ -10107,26 +10115,26 @@
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>Recruitment Calendar</t>
+          <t>Download Admission Certificate</t>
         </is>
       </c>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Attestation &amp; Bio Data Form</t>
+          <t>Transparency &amp; Objectivity</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr"/>
       <c r="D162" s="2" t="inlineStr"/>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=M4ZLp2jMx/L7RLr5Gfi2Eg==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=jWDzPJrrf4pbXjUrVhA7Hg==</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -10154,7 +10162,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -10164,14 +10172,14 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>Attestation &amp; Bio Data Form</t>
+          <t>Transparency &amp; Objectivity</t>
         </is>
       </c>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Usage Terms &amp; Conditions</t>
+          <t>Recruitment Calendar</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -10183,50 +10191,164 @@
       <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="2" t="inlineStr">
         <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=N5n/48rKoj1sNGZtqat51w==</t>
+        </is>
+      </c>
+      <c r="F163" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G163" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H163" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J163" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="30" customHeight="1">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>Attestation &amp; Bio Data Form</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr"/>
+      <c r="D164" s="2" t="inlineStr"/>
+      <c r="E164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=M4ZLp2jMx/L7RLr5Gfi2Eg==</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>Attestation &amp; Bio Data Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Usage Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
           <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=wmpmoV8VNcfB9LTvZnxjTQ==</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr">
         <is>
           <t>OPSC</t>
         </is>
       </c>
-      <c r="H163" s="2" t="inlineStr">
-        <is>
-          <t>General/Other</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J163" s="2" t="inlineStr">
-        <is>
-          <t>Avoid or Closed</t>
-        </is>
-      </c>
-      <c r="K163" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
         <is>
           <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
-      <c r="L163" s="2" t="inlineStr">
+      <c r="L165" s="2" t="inlineStr">
         <is>
           <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
         </is>
       </c>
-      <c r="M163" s="2" t="inlineStr">
+      <c r="M165" s="2" t="inlineStr">
         <is>
           <t>Usage Terms &amp; Conditions</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M163"/>
+  <autoFilter ref="A1:M165"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10237,7 +10359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M164"/>
+  <dimension ref="A1:M166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -12187,7 +12309,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
+          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -12197,17 +12319,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-47bdf7690092/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-4c3834130095/publicNotice</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -12245,14 +12367,14 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA | 2026-07-09</t>
+          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-10</t>
         </is>
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 | 2026-07-14</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -12262,17 +12384,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-4c3834130095/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-606f6f7a0098/publicNotice</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -12310,14 +12432,14 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>POSTPONEMENT NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-10</t>
+          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 | 2026-07-14</t>
         </is>
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 | 2026-07-14</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF FEMALE CONSTABLE AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 02 OF POLICE DEPARTMENT, HARYANA. | 2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -12327,17 +12449,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-606f6f7a0098/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-6b93802b009e/publicNotice</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -12375,14 +12497,14 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>PUBLIC NOTICE TO THE ABSENTEE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 | 2026-07-14</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF FEMALE CONSTABLE AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 02 OF POLICE DEPARTMENT, HARYANA. | 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF FEMALE CONSTABLE AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 02 OF POLICE DEPARTMENT, HARYANA. | 2026</t>
+          <t xml:space="preserve">RE-SCHEDULE NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF </t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -12402,7 +12524,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-6b93802b009e/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-6a467550009b/publicNotice</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -12440,34 +12562,34 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF FEMALE CONSTABLE AGAINST ADVERTISEMENT NO. 01/2026, CATEGORY NO. 02 OF POLICE DEPARTMENT, HARYANA. | 2026-07-16</t>
+          <t>RE-SCHEDULE NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-16</t>
         </is>
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">RE-SCHEDULE NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF </t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE VARIOUS POSTS AGAINST ADVT. NOS. 13/2024, 01/2026 and 06/2026. | 2026-07-22</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-6a467550009b/publicNotice</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9f7f-1923-819f-8af999770001/publicNotice</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -12495,7 +12617,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
@@ -12505,44 +12627,44 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>RE-SCHEDULE NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE POST OF MALE CONSTABLE (GD) AND MALE CONSTABLE (GRP) AGAINST ADVT. NO. 01/2026, CAT. NOS. 01 &amp; 03 OF POLICE DEPARTMENT, HARYANA | 2026-07-16</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL SCREENING TEST (PST) FOR THE VARIOUS POSTS AGAINST ADVT. NOS. 13/2024, 01/2026 and 06/2026. | 2026-07-22</t>
         </is>
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
+          <t>Press release regarding recruitment of Jharkhand Combined Civil Services Main (written) Examination-2025 Advt.No.-01/2026 and Examination Calendar-2026 (22-07-2026)</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>28-01-2026</t>
+          <t>22-07-2026</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>26-02-2026</t>
+          <t>22-07-2026</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/data/Press_Release_01_26_dated_22_07_2026.pdf</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -12560,54 +12682,54 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
+          <t>Press release regarding recruitment of Jharkhand Combined Civil Services Main (written) Examination-2025 Advt.No.-01/2026 and Examination Calendar-2026 (22-07-2026)</t>
         </is>
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>The Jharkhand Examination (Measures Control and Prevention of Unfair Means in Recruitment) Act, 2023 (Jharkhand Act, 15,2023) uploaded date :29-11-2023</t>
+          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>29-11-2023</t>
+          <t>28-01-2026</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>29-11-2023</t>
+          <t>26-02-2026</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/jharkhand%20gazette_29_11_2023.pdf</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -12625,54 +12747,54 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>The Jharkhand Examination (Measures Control and Prevention of Unfair Means in Recruitment) Act, 2023 (Jharkhand Act, 15,2023) uploaded date :29-11-2023</t>
+          <t>Start date for Submission of applications: 28-01-2026 11:30 AM Last date for Submission of applications: 26-02-2026 05:30 PM</t>
         </is>
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 02-10-2023 11:30 Hrs Last date for Submission of applications: 31-10-2023 17:30 Hrs</t>
+          <t>The Jharkhand Examination (Measures Control and Prevention of Unfair Means in Recruitment) Act, 2023 (Jharkhand Act, 15,2023) uploaded date :29-11-2023</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>02-10-2023</t>
+          <t>29-11-2023</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>31-10-2023</t>
+          <t>29-11-2023</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/data/jharkhand%20gazette_29_11_2023.pdf</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -12690,46 +12812,54 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+          <t>Computer/IT/office keywords: it , ai | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>Start date for Submission of applications: 02-10-2023 11:30 Hrs Last date for Submission of applications: 31-10-2023 17:30 Hrs</t>
+          <t>The Jharkhand Examination (Measures Control and Prevention of Unfair Means in Recruitment) Act, 2023 (Jharkhand Act, 15,2023) uploaded date :29-11-2023</t>
         </is>
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Please click here to read the Frequently Asked Question about Recruitment portal.</t>
+          <t>Start date for Submission of applications: 02-10-2023 11:30 Hrs Last date for Submission of applications: 31-10-2023 17:30 Hrs</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>02-10-2023</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>31-10-2023</t>
+        </is>
+      </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>https://recruitment.rajasthan.gov.in/frequentlyaskedquestions</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Rajasthan</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>State Recruitment Portal</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -12747,24 +12877,24 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched | Last date appears closed</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>https://recruitment.rajasthan.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>Please click here to read the Frequently Asked Question about Recruitment portal.</t>
+          <t>Start date for Submission of applications: 02-10-2023 11:30 Hrs Last date for Submission of applications: 31-10-2023 17:30 Hrs</t>
         </is>
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>recruitmenthelpdesk@rajasthan.gov.in</t>
+          <t>Please click here to read the Frequently Asked Question about Recruitment portal.</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -12776,7 +12906,7 @@
       <c r="D41" s="2" t="inlineStr"/>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>mailto:recruitmenthelpdesk@rajasthan.gov.in</t>
+          <t>https://recruitment.rajasthan.gov.in/frequentlyaskedquestions</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -12814,36 +12944,36 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>recruitmenthelpdesk@rajasthan.gov.in</t>
+          <t>Please click here to read the Frequently Asked Question about Recruitment portal.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>S.No | Advertisement Number | Advertisement Name | Registration Start Date | Registration End Date | Application Last Date | Payment Last Day | View Document | Link</t>
+          <t>recruitmenthelpdesk@rajasthan.gov.in</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr"/>
       <c r="D42" s="2" t="inlineStr"/>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>mailto:recruitmenthelpdesk@rajasthan.gov.in</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Rajasthan</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>BTSC</t>
+          <t>State Recruitment Portal</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -12861,24 +12991,24 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment</t>
+          <t>https://recruitment.rajasthan.gov.in/</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>S.No | Advertisement Number | Advertisement Name | Registration Start Date | Registration End Date | Application Last Date | Payment Last Day | View Document | Link</t>
+          <t>recruitmenthelpdesk@rajasthan.gov.in</t>
         </is>
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Advertisement</t>
+          <t>S.No | Advertisement Number | Advertisement Name | Registration Start Date | Registration End Date | Application Last Date | Payment Last Day | View Document | Link</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -12890,7 +13020,7 @@
       <c r="D43" s="2" t="inlineStr"/>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/24_2026.pdf  </t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -12928,7 +13058,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>Advertisement</t>
+          <t>S.No | Advertisement Number | Advertisement Name | Registration Start Date | Registration End Date | Application Last Date | Payment Last Day | View Document | Link</t>
         </is>
       </c>
     </row>
@@ -12947,7 +13077,7 @@
       <c r="D44" s="2" t="inlineStr"/>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/23_2026_0.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/24_2026.pdf  </t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -13004,7 +13134,7 @@
       <c r="D45" s="2" t="inlineStr"/>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/22_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/23_2026_0.pdf  </t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -13061,7 +13191,7 @@
       <c r="D46" s="2" t="inlineStr"/>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/21_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/22_2026.pdf  </t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -13118,7 +13248,7 @@
       <c r="D47" s="2" t="inlineStr"/>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/20_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/21_2026.pdf  </t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -13175,7 +13305,7 @@
       <c r="D48" s="2" t="inlineStr"/>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/19_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/20_2026.pdf  </t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -13232,7 +13362,7 @@
       <c r="D49" s="2" t="inlineStr"/>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/18_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/19_2026.pdf  </t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -13289,7 +13419,7 @@
       <c r="D50" s="2" t="inlineStr"/>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/17_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/18_2026.pdf  </t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -13346,7 +13476,7 @@
       <c r="D51" s="2" t="inlineStr"/>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/16_%202026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/17_2026.pdf  </t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -13403,7 +13533,7 @@
       <c r="D52" s="2" t="inlineStr"/>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/15_2026.pdf  </t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/16_%202026.pdf  </t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -13448,19 +13578,19 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Advertisement</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr"/>
       <c r="D53" s="2" t="inlineStr"/>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment#main-content</t>
+          <t xml:space="preserve">https://btsc.bihar.gov.in/sites/default/files/Advertisement/15_2026.pdf  </t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -13488,7 +13618,7 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
@@ -13498,14 +13628,14 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Advertisement</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Skip to Main Content</t>
+          <t>Skip to main content</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -13517,7 +13647,7 @@
       <c r="D54" s="2" t="inlineStr"/>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/recruitment#wrapper</t>
+          <t>https://btsc.bihar.gov.in/recruitment#main-content</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -13555,26 +13685,26 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Skip to Main Content</t>
+          <t>Skip to main content</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Bihar Technical Service Commission</t>
+          <t>Skip to Main Content</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr"/>
       <c r="D55" s="2" t="inlineStr"/>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/</t>
+          <t>https://btsc.bihar.gov.in/recruitment#wrapper</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -13589,7 +13719,7 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Technical/IT</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
@@ -13602,7 +13732,7 @@
       </c>
       <c r="K55" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
@@ -13612,26 +13742,26 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Bihar Technical Service Commission</t>
+          <t>Skip to Main Content</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Admit Card/Call Letter</t>
+          <t>Bihar Technical Service Commission</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr"/>
       <c r="D56" s="2" t="inlineStr"/>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/admit-card</t>
+          <t>https://btsc.bihar.gov.in/</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -13646,7 +13776,7 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Technical/IT</t>
         </is>
       </c>
       <c r="I56" s="2" t="n">
@@ -13659,7 +13789,7 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
@@ -13669,26 +13799,26 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Admit Card/Call Letter</t>
+          <t>Bihar Technical Service Commission</t>
         </is>
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Admit Card/Call Letter</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr"/>
       <c r="D57" s="2" t="inlineStr"/>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/website-policies</t>
+          <t>https://btsc.bihar.gov.in/admit-card</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -13716,7 +13846,7 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
@@ -13726,26 +13856,26 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Admit Card/Call Letter</t>
         </is>
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Website Policies</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr"/>
       <c r="D58" s="2" t="inlineStr"/>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>https://btsc.bihar.gov.in/disclaimer</t>
+          <t>https://btsc.bihar.gov.in/website-policies</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -13773,7 +13903,7 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
@@ -13783,36 +13913,36 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Website Policies</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconcil</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr"/>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://btsc.bihar.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>UPPSC</t>
+          <t>BTSC</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -13830,36 +13960,36 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
+          <t>https://btsc.bihar.gov.in/recruitment</t>
         </is>
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconciliation | Modification Start Date Last Date | | |</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Notification Based On OTR</t>
+          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconcil</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr"/>
       <c r="D60" s="2" t="inlineStr"/>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>javascript:void();</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -13887,7 +14017,7 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
@@ -13897,14 +14027,14 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>Notification Based On OTR</t>
+          <t>Mode of Recruitment | Examination Name | | Advt. Number Date | Application Filling Start Date | Application Filling Last Date | Fee Deposition Last Date | Last Date of Fee Reconciliation | Modification Start Date Last Date | | |</t>
         </is>
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>View Advertisement</t>
+          <t>Notification Based On OTR</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -13916,7 +14046,7 @@
       <c r="D61" s="2" t="inlineStr"/>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/OuterPages/View_Advertisement.aspx?ID=114&amp;flag=E</t>
+          <t>javascript:void();</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -13954,26 +14084,26 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>View Advertisement</t>
+          <t>Notification Based On OTR</t>
         </is>
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>{{'SiteMap_HM' | translate }}</t>
+          <t>View Advertisement</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr"/>
       <c r="D62" s="2" t="inlineStr"/>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>https://uppsc.up.nic.in/FooterPages/SiteMap.aspx</t>
+          <t>https://uppsc.up.nic.in/OuterPages/View_Advertisement.aspx?ID=114&amp;flag=E</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -14001,7 +14131,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -14011,36 +14141,36 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>{{'SiteMap_HM' | translate }}</t>
+          <t>View Advertisement</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>{{'SiteMap_HM' | translate }}</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr"/>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb-vacancies#main-content</t>
+          <t>https://uppsc.up.nic.in/FooterPages/SiteMap.aspx</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Delhi</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>DSSSB</t>
+          <t>UPPSC</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -14058,36 +14188,36 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb-vacancies</t>
+          <t>https://uppsc.up.nic.in/CandidatePages/Notifications.aspx</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>{{'SiteMap_HM' | translate }}</t>
         </is>
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Skip to main content</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr"/>
       <c r="D64" s="2" t="inlineStr"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/citizen-charter</t>
+          <t>https://dsssb.delhi.gov.in/dsssb-vacancies#main-content</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -14115,7 +14245,7 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
@@ -14125,26 +14255,26 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Skip to main content</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>List of Chairpersons</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr"/>
       <c r="D65" s="2" t="inlineStr"/>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/list-chairpersons</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/citizen-charter</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -14172,7 +14302,7 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
@@ -14182,26 +14312,26 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>List of Chairpersons</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Archived Vacancies</t>
+          <t>List of Chairpersons</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr"/>
       <c r="D66" s="2" t="inlineStr"/>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/archived-vacancies</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/list-chairpersons</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -14229,7 +14359,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -14239,26 +14369,26 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Archived Vacancies</t>
+          <t>List of Chairpersons</t>
         </is>
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Recruitment Rules of Combined Exam</t>
+          <t>Archived Vacancies</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr"/>
       <c r="D67" s="2" t="inlineStr"/>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/recruitment-rules-combined-exam</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/archived-vacancies</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -14286,7 +14416,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -14296,26 +14426,26 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Recruitment Rules of Combined Exam</t>
+          <t>Archived Vacancies</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2018</t>
+          <t>Recruitment Rules of Combined Exam</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr"/>
       <c r="D68" s="2" t="inlineStr"/>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2018</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/recruitment-rules-combined-exam</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -14343,7 +14473,7 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
@@ -14353,14 +14483,14 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2018</t>
+          <t>Recruitment Rules of Combined Exam</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2019</t>
+          <t>Question Bank Online Exam 2018</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -14372,7 +14502,7 @@
       <c r="D69" s="2" t="inlineStr"/>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2019</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2018</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -14410,14 +14540,14 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2019</t>
+          <t>Question Bank Online Exam 2018</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2021</t>
+          <t>Question Bank Online Exam 2019</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -14429,7 +14559,7 @@
       <c r="D70" s="2" t="inlineStr"/>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/dsssb-previous-year-paper-2021</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2019</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -14467,14 +14597,14 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2021</t>
+          <t>Question Bank Online Exam 2019</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2022</t>
+          <t>Question Bank Online Exam 2021</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -14486,7 +14616,7 @@
       <c r="D71" s="2" t="inlineStr"/>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2022</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/dsssb-previous-year-paper-2021</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -14524,14 +14654,14 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2022</t>
+          <t>Question Bank Online Exam 2021</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2023</t>
+          <t>Question Bank Online Exam 2022</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -14543,7 +14673,7 @@
       <c r="D72" s="2" t="inlineStr"/>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2023</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2022</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -14581,14 +14711,14 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2023</t>
+          <t>Question Bank Online Exam 2022</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2024</t>
+          <t>Question Bank Online Exam 2023</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -14600,7 +14730,7 @@
       <c r="D73" s="2" t="inlineStr"/>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2024</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2023</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -14638,14 +14768,14 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2024</t>
+          <t>Question Bank Online Exam 2023</t>
         </is>
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2025</t>
+          <t>Question Bank Online Exam 2024</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -14657,7 +14787,7 @@
       <c r="D74" s="2" t="inlineStr"/>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2025</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2024</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -14695,26 +14825,26 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Question Bank Online Exam 2025</t>
+          <t>Question Bank Online Exam 2024</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>Staff Selection Commission</t>
+          <t>Question Bank Online Exam 2025</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr"/>
       <c r="D75" s="2" t="inlineStr"/>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>https://ssc.nic.in/</t>
+          <t>https://dsssb.delhi.gov.in/doit/tab-content/question-bank-online-exam-2025</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14742,7 +14872,7 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
@@ -14752,14 +14882,14 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Staff Selection Commission</t>
+          <t>Question Bank Online Exam 2025</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>Union Public Service Commission</t>
+          <t>Staff Selection Commission</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -14771,7 +14901,7 @@
       <c r="D76" s="2" t="inlineStr"/>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>https://upsc.gov.in/index.php</t>
+          <t>https://ssc.nic.in/</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14809,26 +14939,26 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Union Public Service Commission</t>
+          <t>Staff Selection Commission</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>Department of Personnel and Training</t>
+          <t>Union Public Service Commission</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr"/>
       <c r="D77" s="2" t="inlineStr"/>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>https://dopt.gov.in/</t>
+          <t>https://upsc.gov.in/index.php</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14856,7 +14986,7 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
@@ -14866,26 +14996,26 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Department of Personnel and Training</t>
+          <t>Union Public Service Commission</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>Recruitments</t>
+          <t>Department of Personnel and Training</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr"/>
       <c r="D78" s="2" t="inlineStr"/>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/recruitment</t>
+          <t>https://dopt.gov.in/</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14913,7 +15043,7 @@
       </c>
       <c r="K78" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L78" s="2" t="inlineStr">
@@ -14923,26 +15053,26 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>Recruitments</t>
+          <t>Department of Personnel and Training</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Recruitments</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr"/>
       <c r="D79" s="2" t="inlineStr"/>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/website-policies</t>
+          <t>https://dsssb.delhi.gov.in/recruitment</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14970,7 +15100,7 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
@@ -14980,14 +15110,14 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>Website Policies</t>
+          <t>Recruitments</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>Feedback (Want to give any suggestion for improvement on our website?)</t>
+          <t>Website Policies</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -14999,7 +15129,7 @@
       <c r="D80" s="2" t="inlineStr"/>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>https://dsssb.delhi.gov.in/dsssb/feedback</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/website-policies</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -15037,26 +15167,26 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>Feedback (Want to give any suggestion for improvement on our website?)</t>
+          <t>Website Policies</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>Vigilance Complaint Information Management System (VCIMS)</t>
+          <t>Feedback (Want to give any suggestion for improvement on our website?)</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr"/>
       <c r="D81" s="2" t="inlineStr"/>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>https://vcims.delhi.gov.in/</t>
+          <t>https://dsssb.delhi.gov.in/dsssb/feedback</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15084,7 +15214,7 @@
       </c>
       <c r="K81" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
@@ -15094,36 +15224,36 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>Vigilance Complaint Information Management System (VCIMS)</t>
+          <t>Feedback (Want to give any suggestion for improvement on our website?)</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>Vigilance Complaint Information Management System (VCIMS)</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr"/>
       <c r="D82" s="2" t="inlineStr"/>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
+          <t>https://vcims.delhi.gov.in/</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Delhi</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>NIELIT Delhi Recruitment</t>
+          <t>DSSSB</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -15141,24 +15271,24 @@
       </c>
       <c r="K82" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/</t>
+          <t>https://dsssb.delhi.gov.in/dsssb-vacancies</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>Vigilance Complaint Information Management System (VCIMS)</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -15170,7 +15300,7 @@
       <c r="D83" s="2" t="inlineStr"/>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15185,7 +15315,7 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I83" s="2" t="n">
@@ -15208,14 +15338,14 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>| STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -15227,7 +15357,7 @@
       <c r="D84" s="2" t="inlineStr"/>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
+          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15242,7 +15372,7 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -15265,14 +15395,14 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>| STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -15284,7 +15414,7 @@
       <c r="D85" s="2" t="inlineStr"/>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15322,14 +15452,14 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
+          <t>| STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -15341,7 +15471,7 @@
       <c r="D86" s="2" t="inlineStr"/>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcd2026</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15356,7 +15486,7 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I86" s="2" t="n">
@@ -15379,14 +15509,14 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
+          <t>STQC Drivers Recruitment 2026 [(Advertisement Number: NIELIT/NDL/STQC/2026/1)]</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -15398,7 +15528,7 @@
       <c r="D87" s="2" t="inlineStr"/>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
+          <t>https://recruit-delhi.nielit.gov.in/frmHome.aspx</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15413,7 +15543,7 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
@@ -15436,36 +15566,36 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
+          <t>STQC Scientific Assistant Recruitment 2025 (Advt. No. NIELIT/NDL/STQC/2025/1)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
+          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr"/>
       <c r="D88" s="2" t="inlineStr"/>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in</t>
+          <t>https://recruit-delhi.nielit.gov.in/stqcgc23/</t>
         </is>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Haryana</t>
+          <t>Central</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>HSSC</t>
+          <t>NIELIT Delhi Recruitment</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -15483,36 +15613,36 @@
       </c>
       <c r="K88" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/</t>
+          <t>https://recruit-delhi.nielit.gov.in/</t>
         </is>
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
+          <t>STQC Group C Recruitment 2023 (Advertisement Number: Advt. No. NIELIT/NDL/STQC/2023/2)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>Apply for CET Group D-05/2026</t>
+          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr"/>
       <c r="D89" s="2" t="inlineStr"/>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>https://onetimeregn.haryana.gov.in/hssc</t>
+          <t>https://hssc.gov.in</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -15540,7 +15670,7 @@
       </c>
       <c r="K89" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L89" s="2" t="inlineStr">
@@ -15550,26 +15680,26 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Apply for CET Group D-05/2026</t>
+          <t>हरियाणा कर्मचारी चयन आयोग Haryana Staff Selection Commission</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Apply for CET Group D-05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr"/>
       <c r="D90" s="2" t="inlineStr"/>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/commission</t>
+          <t>https://onetimeregn.haryana.gov.in/hssc</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
@@ -15597,7 +15727,7 @@
       </c>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr">
@@ -15607,83 +15737,83 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Commission</t>
+          <t>Apply for CET Group D-05/2026</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Commission</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr"/>
       <c r="D91" s="2" t="inlineStr"/>
       <c r="E91" s="2" t="inlineStr">
         <is>
+          <t>https://hssc.gov.in/commission</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Haryana</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>HSSC</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
           <t>https://hssc.gov.in/</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Haryana</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>HSSC</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>General/Other</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>Avoid or Closed</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>https://hssc.gov.in/</t>
-        </is>
-      </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Commission</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr"/>
       <c r="D92" s="2" t="inlineStr"/>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/advertisement</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
@@ -15711,7 +15841,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L92" s="2" t="inlineStr">
@@ -15721,26 +15851,26 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Recruitment</t>
         </is>
       </c>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Advertisements</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr"/>
       <c r="D93" s="2" t="inlineStr"/>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/citizenCharter</t>
+          <t>https://hssc.gov.in/advertisement</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
@@ -15768,7 +15898,7 @@
       </c>
       <c r="K93" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L93" s="2" t="inlineStr">
@@ -15778,26 +15908,26 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Citizen Charter</t>
+          <t>Advertisements</t>
         </is>
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr"/>
       <c r="D94" s="2" t="inlineStr"/>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/notifications</t>
+          <t>https://hssc.gov.in/citizenCharter</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
@@ -15825,7 +15955,7 @@
       </c>
       <c r="K94" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L94" s="2" t="inlineStr">
@@ -15835,14 +15965,14 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Citizen Charter</t>
         </is>
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>Apply Online</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -15854,7 +15984,7 @@
       <c r="D95" s="2" t="inlineStr"/>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/applyOnline</t>
+          <t>https://hssc.gov.in/notifications</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
@@ -15892,26 +16022,26 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Apply Online</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
+          <t>Apply Online</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr"/>
       <c r="D96" s="2" t="inlineStr"/>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-37163ea80089/result</t>
+          <t>https://hssc.gov.in/applyOnline</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
@@ -15939,7 +16069,7 @@
       </c>
       <c r="K96" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L96" s="2" t="inlineStr">
@@ -15949,14 +16079,14 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
+          <t>Apply Online</t>
         </is>
       </c>
     </row>
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
+          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -15968,7 +16098,7 @@
       <c r="D97" s="2" t="inlineStr"/>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2b35286b0083/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-37163ea80089/result</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
@@ -16006,14 +16136,14 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
+          <t>Declaration of revised final result for the post of TGT Science (ROH &amp; Mewat Cadre) against Advt. No. 2/2023, Cat. No. 07 &amp; 12 of Elementary Education Department, Haryana</t>
         </is>
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -16025,7 +16155,7 @@
       <c r="D98" s="2" t="inlineStr"/>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-14153adb0074/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-2b35286b0083/result</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
@@ -16063,26 +16193,26 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR VARIOUS POSTS AGAINST ADVERTISEMENT NO. 06/2026 OF PRISON DEPARTMENT, HARYANA</t>
         </is>
       </c>
     </row>
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social </t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr"/>
       <c r="D99" s="2" t="inlineStr"/>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0315bb59006e/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-14153adb0074/result</t>
         </is>
       </c>
       <c r="F99" s="2" t="inlineStr">
@@ -16110,7 +16240,7 @@
       </c>
       <c r="K99" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L99" s="2" t="inlineStr">
@@ -16120,26 +16250,26 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social Studies (MWT) against Advt. No. 02/2023 and for the posts of TGT Punjabi (ROH) against Advt. No. 04/2023</t>
+          <t>NOTICE TO THE CANDIDATES FOR PHYSICAL MEASUREMENT TEST (PMT) FOR THE VARIOUS POSTS OF VARIOUS DEPARTMENTS AGAINST ADVERTISEMENTS NOS. 13/2024, 02/2026 &amp; 04/2026.</t>
         </is>
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
+          <t xml:space="preserve">Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social </t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr"/>
       <c r="D100" s="2" t="inlineStr"/>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0275db17006b/result</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0315bb59006e/result</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
@@ -16167,7 +16297,7 @@
       </c>
       <c r="K100" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , ai | Specific non-CSE subject appears required | Non-CSE subject risk: physical education</t>
         </is>
       </c>
       <c r="L100" s="2" t="inlineStr">
@@ -16177,14 +16307,14 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
+          <t>Revised Marks for the posts of TGT English (ROH), TGT HOME SCIENCE (ROH &amp; Mewat Cadre), TGT Physical Education (ROH &amp; Mewat Cadre), TGT Sanskrit (ROH &amp; Mewat Cadre) and TGT Social Studies (MWT) against Advt. No. 02/2023 and for the posts of TGT Punjabi (ROH) against Advt. No. 04/2023</t>
         </is>
       </c>
     </row>
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -16196,7 +16326,7 @@
       <c r="D101" s="2" t="inlineStr"/>
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/termsConditions</t>
+          <t>https://hssc.gov.in/file/ac1f23cd-9d9c-1328-819f-0275db17006b/result</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
@@ -16234,14 +16364,14 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>Terms &amp; Conditions</t>
+          <t>Declaration of result for the additional post of Group D vide Advt. 1/2023</t>
         </is>
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Statement</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -16253,7 +16383,7 @@
       <c r="D102" s="2" t="inlineStr"/>
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/accessibilityStatement</t>
+          <t>https://hssc.gov.in/termsConditions</t>
         </is>
       </c>
       <c r="F102" s="2" t="inlineStr">
@@ -16291,26 +16421,26 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>Accessibility Statement</t>
+          <t>Terms &amp; Conditions</t>
         </is>
       </c>
     </row>
     <row r="103" ht="30" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Accessibility Statement</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr"/>
       <c r="D103" s="2" t="inlineStr"/>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>https://hssc.gov.in/disclaimer</t>
+          <t>https://hssc.gov.in/accessibilityStatement</t>
         </is>
       </c>
       <c r="F103" s="2" t="inlineStr">
@@ -16338,7 +16468,7 @@
       </c>
       <c r="K103" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L103" s="2" t="inlineStr">
@@ -16348,14 +16478,14 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>Accessibility Statement</t>
         </is>
       </c>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>Go to main content</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -16367,17 +16497,17 @@
       <c r="D104" s="2" t="inlineStr"/>
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/#container</t>
+          <t>https://hssc.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand</t>
+          <t>Haryana</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>JPSC</t>
+          <t>HSSC</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
@@ -16400,31 +16530,31 @@
       </c>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/</t>
+          <t>https://hssc.gov.in/</t>
         </is>
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>Go to main content</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="105" ht="30" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>Go to main content</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr"/>
       <c r="D105" s="2" t="inlineStr"/>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/university_constituent.php</t>
+          <t>https://www.jpsc.gov.in/#container</t>
         </is>
       </c>
       <c r="F105" s="2" t="inlineStr">
@@ -16452,7 +16582,7 @@
       </c>
       <c r="K105" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L105" s="2" t="inlineStr">
@@ -16462,14 +16592,14 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>Go to main content</t>
         </is>
       </c>
     </row>
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -16481,7 +16611,7 @@
       <c r="D106" s="2" t="inlineStr"/>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/affilated_religious.php</t>
+          <t>https://www.jpsc.gov.in/university_constituent.php</t>
         </is>
       </c>
       <c r="F106" s="2" t="inlineStr">
@@ -16519,14 +16649,14 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -16538,7 +16668,7 @@
       <c r="D107" s="2" t="inlineStr"/>
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/carrer_uni.php</t>
+          <t>https://www.jpsc.gov.in/affilated_religious.php</t>
         </is>
       </c>
       <c r="F107" s="2" t="inlineStr">
@@ -16576,14 +16706,14 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>For University/Constituent College</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -16595,7 +16725,7 @@
       <c r="D108" s="2" t="inlineStr"/>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/carrer_aff.php</t>
+          <t>https://www.jpsc.gov.in/carrer_uni.php</t>
         </is>
       </c>
       <c r="F108" s="2" t="inlineStr">
@@ -16633,14 +16763,14 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
+          <t>For University/Constituent College</t>
         </is>
       </c>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>Merit Promotion Scheme</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -16652,7 +16782,7 @@
       <c r="D109" s="2" t="inlineStr"/>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/merit_promotion_scheme.php</t>
+          <t>https://www.jpsc.gov.in/carrer_aff.php</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
@@ -16690,26 +16820,26 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Merit Promotion Scheme</t>
+          <t>For Affilated/Religious &amp; Linguistic Minority College</t>
         </is>
       </c>
     </row>
     <row r="110" ht="30" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>Online Application Form (OAS)</t>
+          <t>Merit Promotion Scheme</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr"/>
       <c r="D110" s="2" t="inlineStr"/>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/data/FAQ.pdf</t>
+          <t>https://www.jpsc.gov.in/merit_promotion_scheme.php</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
@@ -16737,7 +16867,7 @@
       </c>
       <c r="K110" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L110" s="2" t="inlineStr">
@@ -16747,14 +16877,14 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Online Application Form (OAS)</t>
+          <t>Merit Promotion Scheme</t>
         </is>
       </c>
     </row>
     <row r="111" ht="30" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>Online Application</t>
+          <t>Online Application Form (OAS)</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -16766,7 +16896,7 @@
       <c r="D111" s="2" t="inlineStr"/>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/?click=yes</t>
+          <t>https://www.jpsc.gov.in/data/FAQ.pdf</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
@@ -16804,26 +16934,26 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>Online Application</t>
+          <t>Online Application Form (OAS)</t>
         </is>
       </c>
     </row>
     <row r="112" ht="30" customHeight="1">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>List of Recognised University/Institution</t>
+          <t>Online Application</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr"/>
       <c r="D112" s="2" t="inlineStr"/>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/list_uni.php</t>
+          <t>https://www.jpsc.gov.in/?click=yes</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
@@ -16851,7 +16981,7 @@
       </c>
       <c r="K112" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L112" s="2" t="inlineStr">
@@ -16861,14 +16991,14 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>List of Recognised University/Institution</t>
+          <t>Online Application</t>
         </is>
       </c>
     </row>
     <row r="113" ht="30" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
+          <t>List of Recognised University/Institution</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -16880,7 +17010,7 @@
       <c r="D113" s="2" t="inlineStr"/>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13044</t>
+          <t>https://www.jpsc.gov.in/list_uni.php</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
@@ -16918,14 +17048,14 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
+          <t>List of Recognised University/Institution</t>
         </is>
       </c>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -16937,7 +17067,7 @@
       <c r="D114" s="2" t="inlineStr"/>
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13043</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13044</t>
         </is>
       </c>
       <c r="F114" s="2" t="inlineStr">
@@ -16975,14 +17105,14 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2023 Advt.No.-06/2026</t>
         </is>
       </c>
     </row>
     <row r="115" ht="30" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -16994,7 +17124,7 @@
       <c r="D115" s="2" t="inlineStr"/>
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13039</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13043</t>
         </is>
       </c>
       <c r="F115" s="2" t="inlineStr">
@@ -17032,14 +17162,14 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination (Backlog)-2025 Advt.No.-05/2026</t>
         </is>
       </c>
     </row>
     <row r="116" ht="30" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -17051,7 +17181,7 @@
       <c r="D116" s="2" t="inlineStr"/>
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13038</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13039</t>
         </is>
       </c>
       <c r="F116" s="2" t="inlineStr">
@@ -17089,14 +17219,14 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
+          <t>Recruitment of Jharkhand Combined Civil Services Examination-2025 Advt.No.-01/2026</t>
         </is>
       </c>
     </row>
     <row r="117" ht="30" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
+          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -17108,7 +17238,7 @@
       <c r="D117" s="2" t="inlineStr"/>
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13035</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13038</t>
         </is>
       </c>
       <c r="F117" s="2" t="inlineStr">
@@ -17123,7 +17253,7 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
@@ -17146,14 +17276,14 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
+          <t>Recruitment of Drug Inspector Advt.No.-12/2025</t>
         </is>
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
+          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -17165,7 +17295,7 @@
       <c r="D118" s="2" t="inlineStr"/>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13034</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13035</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
@@ -17180,7 +17310,7 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I118" s="2" t="n">
@@ -17203,14 +17333,14 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
+          <t>Recruitment of Non-Teaching Posts in Universities of Jharkhand. Advt. No. 09/2025</t>
         </is>
       </c>
     </row>
     <row r="119" ht="30" customHeight="1">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Director Advt.No.-07/2025</t>
+          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -17222,7 +17352,7 @@
       <c r="D119" s="2" t="inlineStr"/>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13033</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13034</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
@@ -17260,14 +17390,14 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Director Advt.No.-07/2025</t>
+          <t>Jharkhand Eligibility Test 2024 Advt.No.-08/2025</t>
         </is>
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
+          <t>Recruitment of Director Advt.No.-07/2025</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -17279,7 +17409,7 @@
       <c r="D120" s="2" t="inlineStr"/>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13032</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13033</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
@@ -17317,14 +17447,14 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
+          <t>Recruitment of Director Advt.No.-07/2025</t>
         </is>
       </c>
     </row>
     <row r="121" ht="30" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
+          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -17336,7 +17466,7 @@
       <c r="D121" s="2" t="inlineStr"/>
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13031</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13032</t>
         </is>
       </c>
       <c r="F121" s="2" t="inlineStr">
@@ -17374,14 +17504,14 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
+          <t>Recruitment of Boiler Inspector Advt.No.-02/2025</t>
         </is>
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
+          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -17393,7 +17523,7 @@
       <c r="D122" s="2" t="inlineStr"/>
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13030</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13031</t>
         </is>
       </c>
       <c r="F122" s="2" t="inlineStr">
@@ -17408,7 +17538,7 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -17431,14 +17561,14 @@
       </c>
       <c r="M122" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
+          <t>Recruitment of Inspector of Factories Advt.No.-01/2025</t>
         </is>
       </c>
     </row>
     <row r="123" ht="30" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -17450,7 +17580,7 @@
       <c r="D123" s="2" t="inlineStr"/>
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13029</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13030</t>
         </is>
       </c>
       <c r="F123" s="2" t="inlineStr">
@@ -17488,14 +17618,14 @@
       </c>
       <c r="M123" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Regular),Advt.No.-06/2025</t>
         </is>
       </c>
     </row>
     <row r="124" ht="30" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -17507,7 +17637,7 @@
       <c r="D124" s="2" t="inlineStr"/>
       <c r="E124" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13028</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13029</t>
         </is>
       </c>
       <c r="F124" s="2" t="inlineStr">
@@ -17522,7 +17652,7 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
@@ -17545,14 +17675,14 @@
       </c>
       <c r="M124" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
+          <t>Recruitment of Assistant Public Prosecutor (Backlog),Advt.No.-05/2025</t>
         </is>
       </c>
     </row>
     <row r="125" ht="30" customHeight="1">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
+          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -17564,7 +17694,7 @@
       <c r="D125" s="2" t="inlineStr"/>
       <c r="E125" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13026</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13028</t>
         </is>
       </c>
       <c r="F125" s="2" t="inlineStr">
@@ -17602,14 +17732,14 @@
       </c>
       <c r="M125" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
+          <t>Recruitment of Project Manager and equivalent,advt.No.-04/2025</t>
         </is>
       </c>
     </row>
     <row r="126" ht="30" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
+          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -17621,7 +17751,7 @@
       <c r="D126" s="2" t="inlineStr"/>
       <c r="E126" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13025</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13026</t>
         </is>
       </c>
       <c r="F126" s="2" t="inlineStr">
@@ -17659,14 +17789,14 @@
       </c>
       <c r="M126" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
+          <t>Recruitment of Food Analyst,Advt. No.-05/2024</t>
         </is>
       </c>
     </row>
     <row r="127" ht="30" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
+          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -17678,7 +17808,7 @@
       <c r="D127" s="2" t="inlineStr"/>
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13024</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13025</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
@@ -17693,7 +17823,7 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Office/Clerical</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I127" s="2" t="n">
@@ -17716,14 +17846,14 @@
       </c>
       <c r="M127" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
+          <t>Recruitment of Forest Range Officer,Advt.No.-04/2024</t>
         </is>
       </c>
     </row>
     <row r="128" ht="30" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
+          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -17735,7 +17865,7 @@
       <c r="D128" s="2" t="inlineStr"/>
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13021</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13024</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
@@ -17750,7 +17880,7 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>Office/Clerical</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
@@ -17773,14 +17903,14 @@
       </c>
       <c r="M128" s="2" t="inlineStr">
         <is>
-          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
+          <t>Recruitment of Assistant Conservator of Forest,Advt.No.-03/2024</t>
         </is>
       </c>
     </row>
     <row r="129" ht="30" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
+          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -17792,7 +17922,7 @@
       <c r="D129" s="2" t="inlineStr"/>
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=13020</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13021</t>
         </is>
       </c>
       <c r="F129" s="2" t="inlineStr">
@@ -17807,7 +17937,7 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I129" s="2" t="n">
@@ -17830,14 +17960,14 @@
       </c>
       <c r="M129" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
+          <t>Recruitment for Non-Teaching Posts in Universities of Jharkhand, Advt. No.23/2023</t>
         </is>
       </c>
     </row>
     <row r="130" ht="30" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
+          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -17849,7 +17979,7 @@
       <c r="D130" s="2" t="inlineStr"/>
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=140</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=13020</t>
         </is>
       </c>
       <c r="F130" s="2" t="inlineStr">
@@ -17864,7 +17994,7 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
@@ -17887,14 +18017,14 @@
       </c>
       <c r="M130" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
+          <t>Recruitment of Civil Judge (Junior Division),Advt.No.-22/2023</t>
         </is>
       </c>
     </row>
     <row r="131" ht="30" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -17906,7 +18036,7 @@
       <c r="D131" s="2" t="inlineStr"/>
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=134</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=140</t>
         </is>
       </c>
       <c r="F131" s="2" t="inlineStr">
@@ -17944,14 +18074,14 @@
       </c>
       <c r="M131" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-17/2023</t>
         </is>
       </c>
     </row>
     <row r="132" ht="30" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -17963,7 +18093,7 @@
       <c r="D132" s="2" t="inlineStr"/>
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=133</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=134</t>
         </is>
       </c>
       <c r="F132" s="2" t="inlineStr">
@@ -18001,26 +18131,26 @@
       </c>
       <c r="M132" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
+          <t>Recruitment of Associate Professor-cum-Senior Scientist (Regular),Advt.No.-11/2023</t>
         </is>
       </c>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
+          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr"/>
       <c r="D133" s="2" t="inlineStr"/>
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=120</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=133</t>
         </is>
       </c>
       <c r="F133" s="2" t="inlineStr">
@@ -18035,7 +18165,7 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
@@ -18048,7 +18178,7 @@
       </c>
       <c r="K133" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L133" s="2" t="inlineStr">
@@ -18058,14 +18188,14 @@
       </c>
       <c r="M133" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
+          <t>Recruitment of university Professor-cum-chief Scientist (Regular),Advt.No.-10/2023</t>
         </is>
       </c>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
+          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -18077,7 +18207,7 @@
       <c r="D134" s="2" t="inlineStr"/>
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=119</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=120</t>
         </is>
       </c>
       <c r="F134" s="2" t="inlineStr">
@@ -18115,14 +18245,14 @@
       </c>
       <c r="M134" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
+          <t>Recruitment of Unani Medical Officer (Regular),Advt.No.-11/2022</t>
         </is>
       </c>
     </row>
     <row r="135" ht="30" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
+          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -18134,7 +18264,7 @@
       <c r="D135" s="2" t="inlineStr"/>
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=118</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=119</t>
         </is>
       </c>
       <c r="F135" s="2" t="inlineStr">
@@ -18172,26 +18302,26 @@
       </c>
       <c r="M135" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
+          <t>Recruitment of Homeopathic Medical Officer (Regular),Advt.No.-10/2022</t>
         </is>
       </c>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
+          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr"/>
       <c r="D136" s="2" t="inlineStr"/>
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=82</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=118</t>
         </is>
       </c>
       <c r="F136" s="2" t="inlineStr">
@@ -18219,7 +18349,7 @@
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: medical officer</t>
         </is>
       </c>
       <c r="L136" s="2" t="inlineStr">
@@ -18229,26 +18359,26 @@
       </c>
       <c r="M136" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
+          <t>Recruitment of Ayurvedic Medical Officer (Regular),Advt.No.-09/2022</t>
         </is>
       </c>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
+          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr"/>
       <c r="D137" s="2" t="inlineStr"/>
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=66</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=82</t>
         </is>
       </c>
       <c r="F137" s="2" t="inlineStr">
@@ -18263,7 +18393,7 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
@@ -18276,7 +18406,7 @@
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L137" s="2" t="inlineStr">
@@ -18286,26 +18416,26 @@
       </c>
       <c r="M137" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
+          <t>Recruitment of 6th limited Deputy Collector, Advt. No.11/2018</t>
         </is>
       </c>
     </row>
     <row r="138" ht="30" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
+          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr"/>
       <c r="D138" s="2" t="inlineStr"/>
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=62</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=66</t>
         </is>
       </c>
       <c r="F138" s="2" t="inlineStr">
@@ -18333,7 +18463,7 @@
       </c>
       <c r="K138" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="L138" s="2" t="inlineStr">
@@ -18343,14 +18473,14 @@
       </c>
       <c r="M138" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
+          <t>Recruitment of Associate Professor-Cum-Senior Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No.23/2017</t>
         </is>
       </c>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
+          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -18362,7 +18492,7 @@
       <c r="D139" s="2" t="inlineStr"/>
       <c r="E139" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=61</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=62</t>
         </is>
       </c>
       <c r="F139" s="2" t="inlineStr">
@@ -18377,7 +18507,7 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
@@ -18400,26 +18530,26 @@
       </c>
       <c r="M139" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
+          <t>Recruitment of Associate Professor cum Senior Scientist in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 19/2017</t>
         </is>
       </c>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
+          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr"/>
       <c r="D140" s="2" t="inlineStr"/>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=51</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=61</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -18434,7 +18564,7 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>General/Other</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
@@ -18447,7 +18577,7 @@
       </c>
       <c r="K140" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: agriculture</t>
         </is>
       </c>
       <c r="L140" s="2" t="inlineStr">
@@ -18457,26 +18587,26 @@
       </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
+          <t>Recruitment of Dean in Ranchi Agriculture College Under Birsa Agricultural University, Advt. No. 18/2017.</t>
         </is>
       </c>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
+          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr"/>
       <c r="D141" s="2" t="inlineStr"/>
       <c r="E141" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=40</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=51</t>
         </is>
       </c>
       <c r="F141" s="2" t="inlineStr">
@@ -18504,7 +18634,7 @@
       </c>
       <c r="K141" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Specific non-CSE subject appears required | Non-CSE subject risk: veterinary</t>
         </is>
       </c>
       <c r="L141" s="2" t="inlineStr">
@@ -18514,14 +18644,14 @@
       </c>
       <c r="M141" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
+          <t>Recruitment of University Professor-Cum-Chief Scientist in Ranchi Veterinary College Under Birsa Agricultural University, Advt. No. 08/2017</t>
         </is>
       </c>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
+          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -18533,7 +18663,7 @@
       <c r="D142" s="2" t="inlineStr"/>
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in/exam_files.php?id=39</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=40</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
@@ -18571,26 +18701,26 @@
       </c>
       <c r="M142" s="2" t="inlineStr">
         <is>
-          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
+          <t>Recruitment of Associate Professors in all universities of Jharkhand, Advt No.-41/2016</t>
         </is>
       </c>
     </row>
     <row r="143" ht="30" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>Email Login</t>
+          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr"/>
       <c r="D143" s="2" t="inlineStr"/>
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>https://www.jpsc.gov.in:2096/</t>
+          <t>https://www.jpsc.gov.in/exam_files.php?id=39</t>
         </is>
       </c>
       <c r="F143" s="2" t="inlineStr">
@@ -18605,7 +18735,7 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>General/Other</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
@@ -18618,7 +18748,7 @@
       </c>
       <c r="K143" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L143" s="2" t="inlineStr">
@@ -18628,36 +18758,36 @@
       </c>
       <c r="M143" s="2" t="inlineStr">
         <is>
-          <t>Email Login</t>
+          <t>Recruitment of Professors in all universities of Jharkhand, Advt No.-40/2016</t>
         </is>
       </c>
     </row>
     <row r="144" ht="30" customHeight="1">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>Title | Category Number | Last date</t>
+          <t>Email Login</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr"/>
       <c r="D144" s="2" t="inlineStr"/>
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications</t>
+          <t>https://www.jpsc.gov.in:2096/</t>
         </is>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
-          <t>Kerala</t>
+          <t>Jharkhand</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Kerala PSC</t>
+          <t>JPSC</t>
         </is>
       </c>
       <c r="H144" s="2" t="inlineStr">
@@ -18675,36 +18805,36 @@
       </c>
       <c r="K144" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L144" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications</t>
+          <t>https://www.jpsc.gov.in/</t>
         </is>
       </c>
       <c r="M144" s="2" t="inlineStr">
         <is>
-          <t>Title | Category Number | Last date</t>
+          <t>Email Login</t>
         </is>
       </c>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Title | Category Number | Last date</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr"/>
       <c r="D145" s="2" t="inlineStr"/>
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/notifications#main-content</t>
+          <t>https://www.keralapsc.gov.in/notifications</t>
         </is>
       </c>
       <c r="F145" s="2" t="inlineStr">
@@ -18732,7 +18862,7 @@
       </c>
       <c r="K145" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L145" s="2" t="inlineStr">
@@ -18742,26 +18872,26 @@
       </c>
       <c r="M145" s="2" t="inlineStr">
         <is>
-          <t>Skip to main content</t>
+          <t>Title | Category Number | Last date</t>
         </is>
       </c>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>Answer key-Online Exam</t>
+          <t>Skip to main content</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr"/>
       <c r="D146" s="2" t="inlineStr"/>
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/answerkey_onlineexams</t>
+          <t>https://www.keralapsc.gov.in/notifications#main-content</t>
         </is>
       </c>
       <c r="F146" s="2" t="inlineStr">
@@ -18789,7 +18919,7 @@
       </c>
       <c r="K146" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L146" s="2" t="inlineStr">
@@ -18799,26 +18929,26 @@
       </c>
       <c r="M146" s="2" t="inlineStr">
         <is>
-          <t>Answer key-Online Exam</t>
+          <t>Skip to main content</t>
         </is>
       </c>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>Details of Advice</t>
+          <t>Answer key-Online Exam</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr"/>
       <c r="D147" s="2" t="inlineStr"/>
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/status_of_advice</t>
+          <t>https://www.keralapsc.gov.in/index.php/answerkey_onlineexams</t>
         </is>
       </c>
       <c r="F147" s="2" t="inlineStr">
@@ -18846,7 +18976,7 @@
       </c>
       <c r="K147" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L147" s="2" t="inlineStr">
@@ -18856,14 +18986,14 @@
       </c>
       <c r="M147" s="2" t="inlineStr">
         <is>
-          <t>Details of Advice</t>
+          <t>Answer key-Online Exam</t>
         </is>
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>Candidates Registration</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -18875,7 +19005,7 @@
       <c r="D148" s="2" t="inlineStr"/>
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/registration-thrown-out-candidates</t>
+          <t>https://www.keralapsc.gov.in/index.php/notifications</t>
         </is>
       </c>
       <c r="F148" s="2" t="inlineStr">
@@ -18913,26 +19043,26 @@
       </c>
       <c r="M148" s="2" t="inlineStr">
         <is>
-          <t>Candidates Registration</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
     <row r="149" ht="30" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>General Conditions</t>
+          <t>Details of Advice</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr"/>
       <c r="D149" s="2" t="inlineStr"/>
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/general-conditions</t>
+          <t>https://www.keralapsc.gov.in/index.php/status_of_advice</t>
         </is>
       </c>
       <c r="F149" s="2" t="inlineStr">
@@ -18960,7 +19090,7 @@
       </c>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
@@ -18970,26 +19100,26 @@
       </c>
       <c r="M149" s="2" t="inlineStr">
         <is>
-          <t>General Conditions</t>
+          <t>Details of Advice</t>
         </is>
       </c>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>Terms and Condition</t>
+          <t>Candidates Registration</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr"/>
       <c r="D150" s="2" t="inlineStr"/>
       <c r="E150" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/terms-and-condition</t>
+          <t>https://www.keralapsc.gov.in/index.php/registration-thrown-out-candidates</t>
         </is>
       </c>
       <c r="F150" s="2" t="inlineStr">
@@ -19017,7 +19147,7 @@
       </c>
       <c r="K150" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L150" s="2" t="inlineStr">
@@ -19027,26 +19157,26 @@
       </c>
       <c r="M150" s="2" t="inlineStr">
         <is>
-          <t>Terms and Condition</t>
+          <t>Candidates Registration</t>
         </is>
       </c>
     </row>
     <row r="151" ht="30" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>General Conditions</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr"/>
       <c r="D151" s="2" t="inlineStr"/>
       <c r="E151" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/disclaimer</t>
+          <t>https://www.keralapsc.gov.in/index.php/general-conditions</t>
         </is>
       </c>
       <c r="F151" s="2" t="inlineStr">
@@ -19074,7 +19204,7 @@
       </c>
       <c r="K151" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L151" s="2" t="inlineStr">
@@ -19084,26 +19214,26 @@
       </c>
       <c r="M151" s="2" t="inlineStr">
         <is>
-          <t>Disclaimer</t>
+          <t>General Conditions</t>
         </is>
       </c>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>Digital Personal Data Protection Policy/Privacy Policy</t>
+          <t>Terms and Condition</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , data | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr"/>
       <c r="D152" s="2" t="inlineStr"/>
       <c r="E152" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/privacy-policy</t>
+          <t>https://www.keralapsc.gov.in/terms-and-condition</t>
         </is>
       </c>
       <c r="F152" s="2" t="inlineStr">
@@ -19131,7 +19261,7 @@
       </c>
       <c r="K152" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , data | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L152" s="2" t="inlineStr">
@@ -19141,26 +19271,26 @@
       </c>
       <c r="M152" s="2" t="inlineStr">
         <is>
-          <t>Digital Personal Data Protection Policy/Privacy Policy</t>
+          <t>Terms and Condition</t>
         </is>
       </c>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>Visit Old Website</t>
+          <t>Disclaimer</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr"/>
       <c r="D153" s="2" t="inlineStr"/>
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>https://www.keralapsc.gov.in/old-website-temporarily-shutdown</t>
+          <t>https://www.keralapsc.gov.in/disclaimer</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
@@ -19188,7 +19318,7 @@
       </c>
       <c r="K153" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L153" s="2" t="inlineStr">
@@ -19198,36 +19328,36 @@
       </c>
       <c r="M153" s="2" t="inlineStr">
         <is>
-          <t>Visit Old Website</t>
+          <t>Disclaimer</t>
         </is>
       </c>
     </row>
     <row r="154" ht="30" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>Skip to Main Content</t>
+          <t>Digital Personal Data Protection Policy/Privacy Policy</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , data | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr"/>
       <c r="D154" s="2" t="inlineStr"/>
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx#data</t>
+          <t>https://www.keralapsc.gov.in/privacy-policy</t>
         </is>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="G154" s="2" t="inlineStr">
         <is>
-          <t>OPSC</t>
+          <t>Kerala PSC</t>
         </is>
       </c>
       <c r="H154" s="2" t="inlineStr">
@@ -19245,46 +19375,46 @@
       </c>
       <c r="K154" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , data | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L154" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+          <t>https://www.keralapsc.gov.in/notifications</t>
         </is>
       </c>
       <c r="M154" s="2" t="inlineStr">
         <is>
-          <t>Skip to Main Content</t>
+          <t>Digital Personal Data Protection Policy/Privacy Policy</t>
         </is>
       </c>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>Vision &amp; Mission</t>
+          <t>Visit Old Website</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr"/>
       <c r="D155" s="2" t="inlineStr"/>
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=2UwI/bnoe0Bk6sAjqEVqwQ==</t>
+          <t>https://www.keralapsc.gov.in/old-website-temporarily-shutdown</t>
         </is>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Kerala</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>OPSC</t>
+          <t>Kerala PSC</t>
         </is>
       </c>
       <c r="H155" s="2" t="inlineStr">
@@ -19302,36 +19432,36 @@
       </c>
       <c r="K155" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it , web | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L155" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+          <t>https://www.keralapsc.gov.in/notifications</t>
         </is>
       </c>
       <c r="M155" s="2" t="inlineStr">
         <is>
-          <t>Vision &amp; Mission</t>
+          <t>Visit Old Website</t>
         </is>
       </c>
     </row>
     <row r="156" ht="30" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>Commission &amp; Incumbency Chart</t>
+          <t>Skip to Main Content</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr"/>
       <c r="D156" s="2" t="inlineStr"/>
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=ZJj9IBSdU7Y1yw0WvPyFPw==</t>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx#data</t>
         </is>
       </c>
       <c r="F156" s="2" t="inlineStr">
@@ -19359,7 +19489,7 @@
       </c>
       <c r="K156" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: ai | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L156" s="2" t="inlineStr">
@@ -19369,26 +19499,26 @@
       </c>
       <c r="M156" s="2" t="inlineStr">
         <is>
-          <t>Commission &amp; Incumbency Chart</t>
+          <t>Skip to Main Content</t>
         </is>
       </c>
     </row>
     <row r="157" ht="30" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>Submit Objection / Suggestion</t>
+          <t>Vision &amp; Mission</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr"/>
       <c r="D157" s="2" t="inlineStr"/>
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl59','')</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=2UwI/bnoe0Bk6sAjqEVqwQ==</t>
         </is>
       </c>
       <c r="F157" s="2" t="inlineStr">
@@ -19416,7 +19546,7 @@
       </c>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L157" s="2" t="inlineStr">
@@ -19426,26 +19556,26 @@
       </c>
       <c r="M157" s="2" t="inlineStr">
         <is>
-          <t>Submit Objection / Suggestion</t>
+          <t>Vision &amp; Mission</t>
         </is>
       </c>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Commission &amp; Incumbency Chart</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr"/>
       <c r="D158" s="2" t="inlineStr"/>
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=MeNGKau42B9VX4Nn6oZfXA==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=ZJj9IBSdU7Y1yw0WvPyFPw==</t>
         </is>
       </c>
       <c r="F158" s="2" t="inlineStr">
@@ -19473,7 +19603,7 @@
       </c>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L158" s="2" t="inlineStr">
@@ -19483,26 +19613,26 @@
       </c>
       <c r="M158" s="2" t="inlineStr">
         <is>
-          <t>Advertisements</t>
+          <t>Commission &amp; Incumbency Chart</t>
         </is>
       </c>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Submit Objection / Suggestion</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr"/>
       <c r="D159" s="2" t="inlineStr"/>
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=iQvy8ONZ1XeCyxFZaY2SfA==</t>
+          <t>javascript:__doPostBack('ctl00$generic_masterpage1$ctl59','')</t>
         </is>
       </c>
       <c r="F159" s="2" t="inlineStr">
@@ -19530,7 +19660,7 @@
       </c>
       <c r="K159" s="2" t="inlineStr">
         <is>
-          <t>Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L159" s="2" t="inlineStr">
@@ -19540,26 +19670,26 @@
       </c>
       <c r="M159" s="2" t="inlineStr">
         <is>
-          <t>Notifications</t>
+          <t>Submit Objection / Suggestion</t>
         </is>
       </c>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>Download Admission Certificate</t>
+          <t>Advertisements</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr"/>
       <c r="D160" s="2" t="inlineStr"/>
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=VO/uz97buK3DBoFIVkTEOw==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=MeNGKau42B9VX4Nn6oZfXA==</t>
         </is>
       </c>
       <c r="F160" s="2" t="inlineStr">
@@ -19587,7 +19717,7 @@
       </c>
       <c r="K160" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L160" s="2" t="inlineStr">
@@ -19597,26 +19727,26 @@
       </c>
       <c r="M160" s="2" t="inlineStr">
         <is>
-          <t>Download Admission Certificate</t>
+          <t>Advertisements</t>
         </is>
       </c>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>Transparency &amp; Objectivity</t>
+          <t>Notifications</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr"/>
       <c r="D161" s="2" t="inlineStr"/>
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=jWDzPJrrf4pbXjUrVhA7Hg==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=iQvy8ONZ1XeCyxFZaY2SfA==</t>
         </is>
       </c>
       <c r="F161" s="2" t="inlineStr">
@@ -19644,7 +19774,7 @@
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L161" s="2" t="inlineStr">
@@ -19654,26 +19784,26 @@
       </c>
       <c r="M161" s="2" t="inlineStr">
         <is>
-          <t>Transparency &amp; Objectivity</t>
+          <t>Notifications</t>
         </is>
       </c>
     </row>
     <row r="162" ht="30" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>Recruitment Calendar</t>
+          <t>Download Admission Certificate</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr"/>
       <c r="D162" s="2" t="inlineStr"/>
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=N5n/48rKoj1sNGZtqat51w==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=VO/uz97buK3DBoFIVkTEOw==</t>
         </is>
       </c>
       <c r="F162" s="2" t="inlineStr">
@@ -19701,7 +19831,7 @@
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: mis | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L162" s="2" t="inlineStr">
@@ -19711,26 +19841,26 @@
       </c>
       <c r="M162" s="2" t="inlineStr">
         <is>
-          <t>Recruitment Calendar</t>
+          <t>Download Admission Certificate</t>
         </is>
       </c>
     </row>
     <row r="163" ht="30" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>Attestation &amp; Bio Data Form</t>
+          <t>Transparency &amp; Objectivity</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>Auto-extracted: Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr"/>
       <c r="D163" s="2" t="inlineStr"/>
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=M4ZLp2jMx/L7RLr5Gfi2Eg==</t>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=jWDzPJrrf4pbXjUrVhA7Hg==</t>
         </is>
       </c>
       <c r="F163" s="2" t="inlineStr">
@@ -19758,7 +19888,7 @@
       </c>
       <c r="K163" s="2" t="inlineStr">
         <is>
-          <t>Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
       <c r="L163" s="2" t="inlineStr">
@@ -19768,14 +19898,14 @@
       </c>
       <c r="M163" s="2" t="inlineStr">
         <is>
-          <t>Attestation &amp; Bio Data Form</t>
+          <t>Transparency &amp; Objectivity</t>
         </is>
       </c>
     </row>
     <row r="164" ht="30" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>Usage Terms &amp; Conditions</t>
+          <t>Recruitment Calendar</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -19787,50 +19917,164 @@
       <c r="D164" s="2" t="inlineStr"/>
       <c r="E164" s="2" t="inlineStr">
         <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=N5n/48rKoj1sNGZtqat51w==</t>
+        </is>
+      </c>
+      <c r="F164" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G164" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J164" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>Recruitment Calendar</t>
+        </is>
+      </c>
+    </row>
+    <row r="165" ht="30" customHeight="1">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>Attestation &amp; Bio Data Form</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr"/>
+      <c r="D165" s="2" t="inlineStr"/>
+      <c r="E165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=M4ZLp2jMx/L7RLr5Gfi2Eg==</t>
+        </is>
+      </c>
+      <c r="F165" s="2" t="inlineStr">
+        <is>
+          <t>Odisha</t>
+        </is>
+      </c>
+      <c r="G165" s="2" t="inlineStr">
+        <is>
+          <t>OPSC</t>
+        </is>
+      </c>
+      <c r="H165" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J165" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>Computer/IT/office keywords: data | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>Attestation &amp; Bio Data Form</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="30" customHeight="1">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>Usage Terms &amp; Conditions</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>Auto-extracted: Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr"/>
+      <c r="D166" s="2" t="inlineStr"/>
+      <c r="E166" s="2" t="inlineStr">
+        <is>
           <t>https://www.opsc.gov.in/Public/Pages/View_Content.aspx?id=wmpmoV8VNcfB9LTvZnxjTQ==</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Odisha</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr">
         <is>
           <t>OPSC</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
-        <is>
-          <t>General/Other</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J164" s="2" t="inlineStr">
-        <is>
-          <t>Avoid or Closed</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr">
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>General/Other</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J166" s="2" t="inlineStr">
+        <is>
+          <t>Avoid or Closed</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
         <is>
           <t>Computer/IT/office keywords: it  | Education/subject not clearly matched</t>
         </is>
       </c>
-      <c r="L164" s="2" t="inlineStr">
+      <c r="L166" s="2" t="inlineStr">
         <is>
           <t>https://www.opsc.gov.in/Public/OPSC/Default.aspx</t>
         </is>
       </c>
-      <c r="M164" s="2" t="inlineStr">
+      <c r="M166" s="2" t="inlineStr">
         <is>
           <t>Usage Terms &amp; Conditions</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M164"/>
+  <autoFilter ref="A1:M166"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
